--- a/AAII_Financials/Quarterly/UGRO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UGRO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>UGRO</t>
   </si>
@@ -656,266 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E8" s="3">
         <v>18800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>18300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E9" s="3">
         <v>16000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>14000</v>
       </c>
       <c r="K9" s="3">
         <v>14000</v>
       </c>
       <c r="L9" s="3">
+        <v>14000</v>
+      </c>
+      <c r="M9" s="3">
         <v>9900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -923,73 +933,76 @@
         <v>2800</v>
       </c>
       <c r="E10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F10" s="3">
         <v>2900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2600</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1700</v>
       </c>
       <c r="O10" s="3">
         <v>1700</v>
       </c>
       <c r="P10" s="3">
-        <v>1200</v>
+        <v>1700</v>
       </c>
       <c r="Q10" s="3">
         <v>1200</v>
       </c>
       <c r="R10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S10" s="3">
         <v>1100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,8 +1029,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,11 +1044,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>3300</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1090,8 +1104,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,26 +1181,29 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
         <v>1500</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1700</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
@@ -1194,43 +1214,43 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-1000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>800</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>500</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1238,13 +1258,16 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
         <v>300</v>
@@ -1258,8 +1281,8 @@
       <c r="H15" s="3">
         <v>300</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>8</v>
+      <c r="I15" s="3">
+        <v>300</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>8</v>
@@ -1276,8 +1299,8 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1312,8 +1335,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1363,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E17" s="3">
         <v>24200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>21000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>21900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,8 +1546,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1522,20 +1556,20 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1549,23 +1583,23 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1576,93 +1610,99 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-8200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1300</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-600</v>
       </c>
       <c r="N21" s="3">
         <v>-600</v>
       </c>
       <c r="O21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1670,11 +1710,11 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
@@ -1694,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>1000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>400</v>
       </c>
       <c r="O22" s="3">
         <v>400</v>
@@ -1706,25 +1746,25 @@
         <v>400</v>
       </c>
       <c r="Q22" s="3">
+        <v>400</v>
+      </c>
+      <c r="R22" s="3">
         <v>300</v>
-      </c>
-      <c r="R22" s="3">
-        <v>900</v>
       </c>
       <c r="S22" s="3">
         <v>900</v>
       </c>
       <c r="T22" s="3">
+        <v>900</v>
+      </c>
+      <c r="U22" s="3">
         <v>200</v>
-      </c>
-      <c r="U22" s="3">
-        <v>100</v>
       </c>
       <c r="V22" s="3">
         <v>100</v>
       </c>
       <c r="W22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1735,87 +1775,93 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
         <v>-100</v>
@@ -1833,7 +1879,7 @@
         <v>-100</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1883,8 +1929,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2006,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,8 +2468,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2410,20 +2480,20 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2437,23 +2507,23 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2464,93 +2534,99 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2699,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,82 +2918,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E41" s="3">
         <v>8600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>22800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>27100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>34600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>50400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>49900</v>
-      </c>
-      <c r="N41" s="3">
-        <v>200</v>
       </c>
       <c r="O41" s="3">
         <v>200</v>
       </c>
       <c r="P41" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q41" s="3">
         <v>400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>600</v>
       </c>
-      <c r="Z41" s="3" t="s">
+      <c r="AA41" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2980,82 +3070,88 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E43" s="3">
         <v>22400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>18400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1000</v>
-      </c>
-      <c r="O43" s="3">
-        <v>900</v>
       </c>
       <c r="P43" s="3">
         <v>900</v>
       </c>
       <c r="Q43" s="3">
+        <v>900</v>
+      </c>
+      <c r="R43" s="3">
         <v>1400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1000</v>
-      </c>
-      <c r="X43" s="3">
-        <v>900</v>
       </c>
       <c r="Y43" s="3">
         <v>900</v>
       </c>
-      <c r="Z43" s="3" t="s">
+      <c r="Z43" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA43" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3072,16 +3168,16 @@
         <v>300</v>
       </c>
       <c r="H44" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I44" s="3">
         <v>400</v>
       </c>
       <c r="J44" s="3">
+        <v>400</v>
+      </c>
+      <c r="K44" s="3">
         <v>500</v>
-      </c>
-      <c r="K44" s="3">
-        <v>600</v>
       </c>
       <c r="L44" s="3">
         <v>600</v>
@@ -3090,199 +3186,208 @@
         <v>600</v>
       </c>
       <c r="N44" s="3">
+        <v>600</v>
+      </c>
+      <c r="O44" s="3">
         <v>500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1000</v>
-      </c>
-      <c r="X44" s="3">
-        <v>1200</v>
       </c>
       <c r="Y44" s="3">
         <v>1200</v>
       </c>
-      <c r="Z44" s="3" t="s">
+      <c r="Z44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AA44" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1000</v>
       </c>
-      <c r="Z45" s="3" t="s">
+      <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E46" s="3">
         <v>34500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>36900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>34600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>37300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>44800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>51000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>59500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>54700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>60300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>55200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3700</v>
       </c>
-      <c r="Z46" s="3" t="s">
+      <c r="AA46" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3">
         <v>2600</v>
@@ -3291,10 +3396,10 @@
         <v>2600</v>
       </c>
       <c r="G47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H47" s="3">
         <v>2500</v>
-      </c>
-      <c r="H47" s="3">
-        <v>4200</v>
       </c>
       <c r="I47" s="3">
         <v>4200</v>
@@ -3303,7 +3408,7 @@
         <v>4200</v>
       </c>
       <c r="K47" s="3">
-        <v>1700</v>
+        <v>4200</v>
       </c>
       <c r="L47" s="3">
         <v>1700</v>
@@ -3321,37 +3426,40 @@
         <v>1700</v>
       </c>
       <c r="Q47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="R47" s="3">
         <v>1800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1100</v>
-      </c>
-      <c r="X47" s="3">
-        <v>500</v>
       </c>
       <c r="Y47" s="3">
         <v>500</v>
       </c>
-      <c r="Z47" s="3" t="s">
+      <c r="Z47" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3359,19 +3467,19 @@
         <v>3700</v>
       </c>
       <c r="E48" s="3">
-        <v>3900</v>
+        <v>3700</v>
       </c>
       <c r="F48" s="3">
         <v>3900</v>
       </c>
       <c r="G48" s="3">
+        <v>3900</v>
+      </c>
+      <c r="H48" s="3">
         <v>2000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1600</v>
-      </c>
-      <c r="I48" s="3">
-        <v>900</v>
       </c>
       <c r="J48" s="3">
         <v>900</v>
@@ -3380,16 +3488,16 @@
         <v>900</v>
       </c>
       <c r="L48" s="3">
+        <v>900</v>
+      </c>
+      <c r="M48" s="3">
         <v>100</v>
-      </c>
-      <c r="M48" s="3">
-        <v>200</v>
       </c>
       <c r="N48" s="3">
         <v>200</v>
       </c>
       <c r="O48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>300</v>
@@ -3398,63 +3506,66 @@
         <v>300</v>
       </c>
       <c r="R48" s="3">
+        <v>300</v>
+      </c>
+      <c r="S48" s="3">
         <v>400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>600</v>
-      </c>
-      <c r="V48" s="3">
-        <v>400</v>
       </c>
       <c r="W48" s="3">
         <v>400</v>
       </c>
       <c r="X48" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Y48" s="3">
         <v>300</v>
       </c>
-      <c r="Z48" s="3" t="s">
+      <c r="Z48" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E49" s="3">
         <v>20400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>20700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>21000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10600</v>
-      </c>
-      <c r="L49" s="3">
-        <v>900</v>
       </c>
       <c r="M49" s="3">
         <v>900</v>
@@ -3463,7 +3574,7 @@
         <v>900</v>
       </c>
       <c r="O49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="P49" s="3">
         <v>1000</v>
@@ -3478,13 +3589,13 @@
         <v>1000</v>
       </c>
       <c r="T49" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="U49" s="3">
         <v>900</v>
       </c>
       <c r="V49" s="3">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="W49" s="3">
         <v>100</v>
@@ -3492,14 +3603,17 @@
       <c r="X49" s="3">
         <v>100</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>8</v>
+      <c r="Y49" s="3">
+        <v>100</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,8 +3763,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3672,11 +3792,11 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="L52" s="3">
-        <v>100</v>
       </c>
       <c r="M52" s="3">
         <v>100</v>
@@ -3684,8 +3804,8 @@
       <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>8</v>
+      <c r="O52" s="3">
+        <v>100</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>8</v>
@@ -3693,18 +3813,18 @@
       <c r="Q52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
       </c>
       <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
       <c r="V52" s="3">
         <v>0</v>
       </c>
@@ -3715,13 +3835,16 @@
         <v>0</v>
       </c>
       <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
         <v>100</v>
       </c>
-      <c r="Z52" s="3" t="s">
+      <c r="AA52" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3917,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E54" s="3">
         <v>61300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>64100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>62100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>58400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>66100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>65500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>74200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>68000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>63100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>58000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4600</v>
       </c>
-      <c r="Z54" s="3" t="s">
+      <c r="AA54" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,96 +4054,100 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E57" s="3">
         <v>18600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>7900</v>
       </c>
       <c r="I57" s="3">
         <v>7900</v>
       </c>
       <c r="J57" s="3">
+        <v>7900</v>
+      </c>
+      <c r="K57" s="3">
         <v>6100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>900</v>
       </c>
-      <c r="Z57" s="3" t="s">
+      <c r="AA57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3800</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>8</v>
@@ -4021,8 +4155,8 @@
       <c r="I58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
+      <c r="J58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4031,37 +4165,37 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>1000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3500</v>
-      </c>
-      <c r="W58" s="3">
-        <v>500</v>
       </c>
       <c r="X58" s="3">
         <v>500</v>
@@ -4069,159 +4203,168 @@
       <c r="Y58" s="3">
         <v>500</v>
       </c>
-      <c r="Z58" s="3" t="s">
+      <c r="Z58" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E59" s="3">
         <v>11300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6000</v>
-      </c>
-      <c r="P59" s="3">
-        <v>5400</v>
       </c>
       <c r="Q59" s="3">
         <v>5400</v>
       </c>
       <c r="R59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="S59" s="3">
         <v>4800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5100</v>
       </c>
-      <c r="Z59" s="3" t="s">
+      <c r="AA59" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E60" s="3">
         <v>31800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>24300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>25000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6400</v>
       </c>
-      <c r="Z60" s="3" t="s">
+      <c r="AA60" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4256,32 +4399,32 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>1000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>1800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>200</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4294,49 +4437,52 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E62" s="3">
         <v>2700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1000</v>
       </c>
       <c r="K62" s="3">
         <v>1000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>8</v>
+      <c r="L62" s="3">
+        <v>1000</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
       </c>
       <c r="P62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="3">
         <v>100</v>
@@ -4348,13 +4494,13 @@
         <v>100</v>
       </c>
       <c r="T62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>8</v>
+      <c r="V62" s="3">
+        <v>0</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>8</v>
@@ -4368,8 +4514,11 @@
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4745,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E66" s="3">
         <v>34600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>27300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6400</v>
       </c>
-      <c r="Z66" s="3" t="s">
+      <c r="AA66" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5159,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-52100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-48700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-43300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-38100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-33900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-25300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-23500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-22800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-22200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-22300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-23600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-22000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-20900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-18600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-16900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-14300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-11400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-10000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-8500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z72" s="3" t="s">
+      <c r="AA72" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5467,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E76" s="3">
         <v>26700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>30300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>34700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>37500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>46300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>44600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>48200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>49500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>48600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-7400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-6700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-5600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-5000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-5300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-3000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-3500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-3800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-2700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z76" s="3" t="s">
+      <c r="AA76" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5621,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +5811,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5628,13 +5827,13 @@
         <v>400</v>
       </c>
       <c r="G83" s="3">
+        <v>400</v>
+      </c>
+      <c r="H83" s="3">
         <v>500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>200</v>
       </c>
       <c r="J83" s="3">
         <v>200</v>
@@ -5643,7 +5842,7 @@
         <v>200</v>
       </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
@@ -5673,22 +5872,25 @@
         <v>100</v>
       </c>
       <c r="V83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
       <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6271,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E89" s="3">
         <v>3600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,47 +6379,48 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -6207,25 +6428,25 @@
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-200</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-100</v>
       </c>
       <c r="Y91" s="3">
         <v>-100</v>
@@ -6233,8 +6454,11 @@
       <c r="Z91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,47 +6608,50 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>2100</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
       </c>
       <c r="F94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5700</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -6429,34 +6659,37 @@
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-500</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-200</v>
       </c>
       <c r="V94" s="3">
         <v>-200</v>
       </c>
       <c r="W94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X94" s="3">
         <v>-800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6716,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,82 +7022,88 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-3800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>49400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3000</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y100" s="3">
         <v>100</v>
       </c>
       <c r="Z100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA100" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6927,78 +7176,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E102" s="3">
         <v>1200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>49700</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="P102" s="3">
         <v>-200</v>
       </c>
       <c r="Q102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R102" s="3">
         <v>100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UGRO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UGRO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>UGRO</t>
   </si>
@@ -656,353 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F8" s="3">
         <v>20900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>18800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>16800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>17300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>12400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>16300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>21100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>19000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>18300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>12800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>12000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>9200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>8400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>4000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>7100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>5600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>11500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>5800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>5400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>5300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>9300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>3400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>13300</v>
+      </c>
+      <c r="F9" s="3">
         <v>18100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>16000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>13900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>14100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>9800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>12800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>16200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>14000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>14000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>9900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>9400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>7500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>6700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>3100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>6000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>3700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>7900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>4200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>3900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>3700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>6500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F10" s="3">
         <v>2800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>3200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>3500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>5000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>4300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>2900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>3600</v>
-      </c>
-      <c r="V10" s="3">
-        <v>1600</v>
-      </c>
-      <c r="W10" s="3">
-        <v>1500</v>
       </c>
       <c r="X10" s="3">
         <v>1600</v>
       </c>
       <c r="Y10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AA10" s="3">
         <v>2800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1030,8 +1055,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1047,14 +1074,14 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
-        <v>3300</v>
+      <c r="H12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="J12" s="3">
+        <v>3300</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1107,8 +1134,14 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,32 +1217,38 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>1500</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>1700</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
@@ -1217,52 +1256,58 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-1000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>800</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>500</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1270,10 +1315,10 @@
         <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
         <v>300</v>
@@ -1284,11 +1329,11 @@
       <c r="I15" s="3">
         <v>300</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>8</v>
+      <c r="J15" s="3">
+        <v>300</v>
+      </c>
+      <c r="K15" s="3">
+        <v>300</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>8</v>
@@ -1302,11 +1347,11 @@
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1338,8 +1383,14 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1415,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>19600</v>
+      </c>
+      <c r="F17" s="3">
         <v>24300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>24200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>21800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>21200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>21000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>18200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>21900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>19600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>18200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>11600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>12700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>9500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>8500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>5200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>5700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>8900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>7500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>14100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>7200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>7100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>6200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>10600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>4200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-5400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-5000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-3900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-8600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-2600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-1400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,8 +1612,10 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1559,23 +1626,23 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>-100</v>
       </c>
       <c r="I20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1586,26 +1653,26 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1613,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
@@ -1624,103 +1691,115 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-5000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-4700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-3800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-8200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-1100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-1700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-1800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-2500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-1300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-1700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
@@ -1737,126 +1816,138 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>1000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>400</v>
-      </c>
-      <c r="P22" s="3">
-        <v>400</v>
       </c>
       <c r="Q22" s="3">
         <v>400</v>
       </c>
       <c r="R22" s="3">
+        <v>400</v>
+      </c>
+      <c r="S22" s="3">
+        <v>400</v>
+      </c>
+      <c r="T22" s="3">
         <v>300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-5500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-5200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-4200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-8700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-2600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-2800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-1500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1800</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-800</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-1300</v>
       </c>
       <c r="Z23" s="3">
         <v>-800</v>
       </c>
       <c r="AA23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1864,10 +1955,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
         <v>-100</v>
@@ -1882,10 +1973,10 @@
         <v>-100</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1932,8 +2023,14 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2106,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-5400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-5100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-4200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-8700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-2600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-2800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-2900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1800</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-800</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-1300</v>
       </c>
       <c r="Z26" s="3">
         <v>-800</v>
       </c>
       <c r="AA26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-5400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-5100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-4200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-8700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-2600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-2800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-2900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1800</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-800</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-1300</v>
       </c>
       <c r="Z27" s="3">
         <v>-800</v>
       </c>
       <c r="AA27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2355,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2438,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2521,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,8 +2604,14 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2483,23 +2622,23 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>100</v>
       </c>
       <c r="I32" s="3">
+        <v>300</v>
+      </c>
+      <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2510,26 +2649,26 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2537,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="3">
         <v>0</v>
@@ -2548,85 +2687,97 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-5400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-5100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-4200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-8700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-2600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-2800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-2900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1800</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-800</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-1300</v>
       </c>
       <c r="Z33" s="3">
         <v>-800</v>
       </c>
       <c r="AA33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2853,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-5400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-5100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-4200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-8700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-2600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-2800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-2900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1800</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-800</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-1300</v>
       </c>
       <c r="Z35" s="3">
         <v>-800</v>
       </c>
       <c r="AA35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +3059,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,67 +3090,69 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F41" s="3">
         <v>4800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>8600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>7300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>12000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>18600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>22800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>27100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>34600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>40500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>50400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>49900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>200</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>400</v>
-      </c>
-      <c r="R41" s="3">
-        <v>600</v>
       </c>
       <c r="S41" s="3">
         <v>400</v>
       </c>
       <c r="T41" s="3">
+        <v>600</v>
+      </c>
+      <c r="U41" s="3">
+        <v>400</v>
+      </c>
+      <c r="V41" s="3">
         <v>3500</v>
-      </c>
-      <c r="U41" s="3">
-        <v>1200</v>
-      </c>
-      <c r="V41" s="3">
-        <v>900</v>
       </c>
       <c r="W41" s="3">
         <v>1200</v>
@@ -2988,16 +3161,22 @@
         <v>900</v>
       </c>
       <c r="Y41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z41" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA41" s="3">
         <v>1000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>600</v>
       </c>
-      <c r="AA41" s="3" t="s">
+      <c r="AC41" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3073,93 +3252,105 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>37100</v>
+      </c>
+      <c r="F43" s="3">
         <v>26700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>22400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>24900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>18400</v>
-      </c>
-      <c r="H43" s="3">
-        <v>13500</v>
-      </c>
-      <c r="I43" s="3">
-        <v>15400</v>
       </c>
       <c r="J43" s="3">
         <v>13500</v>
       </c>
       <c r="K43" s="3">
+        <v>15400</v>
+      </c>
+      <c r="L43" s="3">
+        <v>13500</v>
+      </c>
+      <c r="M43" s="3">
         <v>13100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>5800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>900</v>
       </c>
-      <c r="AA43" s="3" t="s">
+      <c r="AC43" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F44" s="3">
         <v>300</v>
@@ -3171,49 +3362,49 @@
         <v>300</v>
       </c>
       <c r="I44" s="3">
+        <v>300</v>
+      </c>
+      <c r="J44" s="3">
+        <v>300</v>
+      </c>
+      <c r="K44" s="3">
         <v>400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>500</v>
-      </c>
-      <c r="L44" s="3">
-        <v>600</v>
-      </c>
-      <c r="M44" s="3">
-        <v>600</v>
       </c>
       <c r="N44" s="3">
         <v>600</v>
       </c>
       <c r="O44" s="3">
+        <v>600</v>
+      </c>
+      <c r="P44" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q44" s="3">
         <v>500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>700</v>
-      </c>
-      <c r="T44" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U44" s="3">
-        <v>1300</v>
       </c>
       <c r="V44" s="3">
         <v>1000</v>
       </c>
       <c r="W44" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="X44" s="3">
         <v>1000</v>
@@ -3222,199 +3413,217 @@
         <v>1200</v>
       </c>
       <c r="Z44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA44" s="3">
         <v>1200</v>
       </c>
-      <c r="AA44" s="3" t="s">
+      <c r="AB44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC44" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F45" s="3">
         <v>3000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>4400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>3800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>4900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>6100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>10100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>11200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>7800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>6200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>3900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>3500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>2500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1000</v>
       </c>
-      <c r="AA45" s="3" t="s">
+      <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>41000</v>
+      </c>
+      <c r="F46" s="3">
         <v>34800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>34500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>36900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>34600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>37300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>44800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>51000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>59500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>54700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>60300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>55200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>5200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>4600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>4400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>5300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>7000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>4900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>4300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3700</v>
       </c>
-      <c r="AA46" s="3" t="s">
+      <c r="AC46" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E47" s="3">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="G47" s="3">
         <v>2600</v>
       </c>
       <c r="H47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J47" s="3">
         <v>2500</v>
-      </c>
-      <c r="I47" s="3">
-        <v>4200</v>
-      </c>
-      <c r="J47" s="3">
-        <v>4200</v>
       </c>
       <c r="K47" s="3">
         <v>4200</v>
       </c>
       <c r="L47" s="3">
-        <v>1700</v>
+        <v>4200</v>
       </c>
       <c r="M47" s="3">
-        <v>1700</v>
+        <v>4200</v>
       </c>
       <c r="N47" s="3">
         <v>1700</v>
@@ -3429,158 +3638,170 @@
         <v>1700</v>
       </c>
       <c r="R47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T47" s="3">
         <v>1800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>2000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>1500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>1300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>1100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>500</v>
       </c>
-      <c r="AA47" s="3" t="s">
+      <c r="AC47" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F48" s="3">
         <v>3700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1600</v>
-      </c>
-      <c r="J48" s="3">
-        <v>900</v>
-      </c>
-      <c r="K48" s="3">
-        <v>900</v>
       </c>
       <c r="L48" s="3">
         <v>900</v>
       </c>
       <c r="M48" s="3">
+        <v>900</v>
+      </c>
+      <c r="N48" s="3">
+        <v>900</v>
+      </c>
+      <c r="O48" s="3">
         <v>100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>200</v>
-      </c>
-      <c r="P48" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>300</v>
       </c>
       <c r="R48" s="3">
         <v>300</v>
       </c>
       <c r="S48" s="3">
+        <v>300</v>
+      </c>
+      <c r="T48" s="3">
+        <v>300</v>
+      </c>
+      <c r="U48" s="3">
         <v>400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>300</v>
       </c>
-      <c r="AA48" s="3" t="s">
+      <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F49" s="3">
         <v>20200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>20400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>20700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>21000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>16600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>15500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>9400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>9600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>10600</v>
-      </c>
-      <c r="M49" s="3">
-        <v>900</v>
-      </c>
-      <c r="N49" s="3">
-        <v>900</v>
       </c>
       <c r="O49" s="3">
         <v>900</v>
       </c>
       <c r="P49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="Q49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="R49" s="3">
         <v>1000</v>
@@ -3592,28 +3813,34 @@
         <v>1000</v>
       </c>
       <c r="U49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W49" s="3">
         <v>900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>900</v>
-      </c>
-      <c r="W49" s="3">
-        <v>100</v>
-      </c>
-      <c r="X49" s="3">
-        <v>100</v>
       </c>
       <c r="Y49" s="3">
         <v>100</v>
       </c>
-      <c r="Z49" s="3" t="s">
+      <c r="Z49" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA49" s="3" t="s">
+      <c r="AC49" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3916,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,8 +3999,14 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3795,42 +4034,42 @@
       <c r="K52" s="3">
         <v>0</v>
       </c>
-      <c r="L52" s="3" t="s">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="M52" s="3">
-        <v>100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>100</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>8</v>
+      <c r="P52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>100</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
         <v>100</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
@@ -3838,13 +4077,19 @@
         <v>0</v>
       </c>
       <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
         <v>100</v>
       </c>
-      <c r="AA52" s="3" t="s">
+      <c r="AC52" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,85 +4165,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>64400</v>
+      </c>
+      <c r="F54" s="3">
         <v>58600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>61300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>64100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>62100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>58400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>66100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>65500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>74200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>68000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>63100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>58000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>8200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>7600</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>7400</v>
-      </c>
-      <c r="R54" s="3">
-        <v>8500</v>
       </c>
       <c r="S54" s="3">
         <v>7400</v>
       </c>
       <c r="T54" s="3">
+        <v>8500</v>
+      </c>
+      <c r="U54" s="3">
+        <v>7400</v>
+      </c>
+      <c r="V54" s="3">
         <v>10100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>8100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>8000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>5700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>5500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>5200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>4600</v>
       </c>
-      <c r="AA54" s="3" t="s">
+      <c r="AC54" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4283,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,316 +4314,342 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>25400</v>
+      </c>
+      <c r="F57" s="3">
         <v>22200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>18600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>14900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>10000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>7900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>7900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>6100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>3800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>3700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>3300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>3400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>900</v>
       </c>
-      <c r="AA57" s="3" t="s">
+      <c r="AC57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F58" s="3">
         <v>2000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3800</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>1000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>7100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>6200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>6000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>3800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>4200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>3200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>3400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>3500</v>
-      </c>
-      <c r="X58" s="3">
-        <v>500</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>500</v>
       </c>
       <c r="Z58" s="3">
         <v>500</v>
       </c>
-      <c r="AA58" s="3" t="s">
+      <c r="AA58" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F59" s="3">
         <v>7800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>11300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>13100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>10500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>12500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>10200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>12100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>18900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>15400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>11300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>6200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>6800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>6000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>5400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>5400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>4800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>5700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>3900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>4400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>4500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>6400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>5700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>5100</v>
       </c>
-      <c r="AA59" s="3" t="s">
+      <c r="AC59" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>42100</v>
+      </c>
+      <c r="F60" s="3">
         <v>31900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>31800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>30900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>24300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>19000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>18200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>20100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>25000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>18200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>13600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>9500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>14500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>9400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>13000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>14000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>12300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>13500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>10300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>11200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>9600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>8100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>7400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>6400</v>
       </c>
-      <c r="AA60" s="3" t="s">
+      <c r="AC60" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4402,35 +4687,35 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>1000</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>1800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>200</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4440,55 +4725,61 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F62" s="3">
         <v>2500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>3100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>2000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1000</v>
       </c>
-      <c r="M62" s="3" t="s">
+      <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N62" s="3" t="s">
+      <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S62" s="3">
         <v>100</v>
@@ -4497,16 +4788,16 @@
         <v>100</v>
       </c>
       <c r="U62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V62" s="3">
-        <v>0</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>8</v>
+        <v>100</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>8</v>
@@ -4517,8 +4808,14 @@
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4891,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4974,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,85 +5057,97 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>44300</v>
+      </c>
+      <c r="F66" s="3">
         <v>34500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>34600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>33800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>27300</v>
-      </c>
-      <c r="H66" s="3">
-        <v>20900</v>
-      </c>
-      <c r="I66" s="3">
-        <v>19800</v>
       </c>
       <c r="J66" s="3">
         <v>20900</v>
       </c>
       <c r="K66" s="3">
+        <v>19800</v>
+      </c>
+      <c r="L66" s="3">
+        <v>20900</v>
+      </c>
+      <c r="M66" s="3">
         <v>26000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>19200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>13600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>9500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>15600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>14300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>14000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>14100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>12400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>15400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>11100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>11500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>9600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>8100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>7400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>6400</v>
       </c>
-      <c r="AA66" s="3" t="s">
+      <c r="AC66" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5175,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5254,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5337,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5420,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,85 +5503,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-58900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-56800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-52100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-48700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-43300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-38100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-33900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-25300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-23500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-22800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-22200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-22300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-23600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-22000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-20200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-18600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-16900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-14300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-11400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-10000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-8500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA72" s="3" t="s">
+      <c r="AC72" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5669,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5752,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,85 +5835,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>20100</v>
+      </c>
+      <c r="F76" s="3">
         <v>24200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>26700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>30300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>34700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>37500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>46300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>44600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>48200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>48800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>49500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>48600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-7400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-6600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-5600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-5000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-5300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-3000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-3500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-3800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA76" s="3" t="s">
+      <c r="AC76" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +6001,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-5400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-5100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-4200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-8700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-2600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-2800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-2900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1800</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-800</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-1300</v>
       </c>
       <c r="Z81" s="3">
         <v>-800</v>
       </c>
       <c r="AA81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AB81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,8 +6207,10 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5830,25 +6227,25 @@
         <v>400</v>
       </c>
       <c r="H83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I83" s="3">
         <v>400</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="K83" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
       </c>
       <c r="M83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
@@ -5875,22 +6272,28 @@
         <v>100</v>
       </c>
       <c r="W83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
         <v>100</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6369,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6452,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6535,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6618,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6701,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>3600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-4300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-4100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-2500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,8 +6819,10 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6389,76 +6830,82 @@
         <v>-200</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-100</v>
       </c>
       <c r="AA91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6981,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,85 +7064,97 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F94" s="3">
         <v>2100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-3100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-2600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-5700</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +7182,10 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6794,8 +7261,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7344,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7427,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,85 +7510,97 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="E100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-2300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-3800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-3200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>49400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>1200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>2000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>1100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>2200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>3000</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7179,81 +7676,93 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-4700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-6600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-4200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-4300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-7500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-5900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-9900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>49700</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-3100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>2300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UGRO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UGRO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>UGRO</t>
   </si>
@@ -955,13 +955,13 @@
         <v>1700</v>
       </c>
       <c r="F10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H10" s="3">
         <v>2800</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2900</v>
       </c>
       <c r="I10" s="3">
         <v>3200</v>
@@ -1080,8 +1080,8 @@
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
-        <v>3300</v>
+      <c r="J12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1240,14 +1240,14 @@
       <c r="G14" s="3">
         <v>1500</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>200</v>
       </c>
       <c r="I14" s="3">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="J14" s="3">
-        <v>1700</v>
+        <v>5000</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1429,19 +1429,19 @@
         <v>19600</v>
       </c>
       <c r="F17" s="3">
-        <v>24300</v>
+        <v>24000</v>
       </c>
       <c r="G17" s="3">
-        <v>24200</v>
+        <v>22700</v>
       </c>
       <c r="H17" s="3">
         <v>21800</v>
       </c>
       <c r="I17" s="3">
-        <v>21200</v>
+        <v>20300</v>
       </c>
       <c r="J17" s="3">
-        <v>21000</v>
+        <v>16000</v>
       </c>
       <c r="K17" s="3">
         <v>18200</v>
@@ -1512,19 +1512,19 @@
         <v>-4600</v>
       </c>
       <c r="F18" s="3">
-        <v>-3400</v>
+        <v>-3100</v>
       </c>
       <c r="G18" s="3">
-        <v>-5400</v>
+        <v>-3900</v>
       </c>
       <c r="H18" s="3">
         <v>-5000</v>
       </c>
       <c r="I18" s="3">
-        <v>-3900</v>
+        <v>-2900</v>
       </c>
       <c r="J18" s="3">
-        <v>-8600</v>
+        <v>-3600</v>
       </c>
       <c r="K18" s="3">
         <v>-1900</v>
@@ -1629,16 +1629,16 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
@@ -1703,25 +1703,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1700</v>
+        <v>-1900</v>
       </c>
       <c r="E21" s="3">
-        <v>-4200</v>
+        <v>-4400</v>
       </c>
       <c r="F21" s="3">
-        <v>-3000</v>
+        <v>-2900</v>
       </c>
       <c r="G21" s="3">
-        <v>-5000</v>
+        <v>-3800</v>
       </c>
       <c r="H21" s="3">
         <v>-4700</v>
       </c>
       <c r="I21" s="3">
-        <v>-3800</v>
+        <v>-2600</v>
       </c>
       <c r="J21" s="3">
-        <v>-8200</v>
+        <v>-3500</v>
       </c>
       <c r="K21" s="3">
         <v>-1400</v>
@@ -2625,16 +2625,16 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
@@ -3267,7 +3267,7 @@
         <v>28900</v>
       </c>
       <c r="E43" s="3">
-        <v>37100</v>
+        <v>34700</v>
       </c>
       <c r="F43" s="3">
         <v>26700</v>
@@ -3279,7 +3279,7 @@
         <v>24900</v>
       </c>
       <c r="I43" s="3">
-        <v>18400</v>
+        <v>16000</v>
       </c>
       <c r="J43" s="3">
         <v>13500</v>
@@ -3430,25 +3430,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J45" s="3">
         <v>3400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>4400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>4900</v>
       </c>
       <c r="K45" s="3">
         <v>6100</v>
@@ -3598,11 +3598,11 @@
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G47" s="3">
         <v>2600</v>
@@ -4010,26 +4010,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4405,25 +4405,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2500</v>
+        <v>3200</v>
       </c>
       <c r="E58" s="3">
-        <v>3200</v>
+        <v>3900</v>
       </c>
       <c r="F58" s="3">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="G58" s="3">
-        <v>1900</v>
+        <v>2600</v>
       </c>
       <c r="H58" s="3">
-        <v>2900</v>
+        <v>3500</v>
       </c>
       <c r="I58" s="3">
-        <v>3800</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
+        <v>4400</v>
+      </c>
+      <c r="J58" s="3">
+        <v>400</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
@@ -4488,25 +4488,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>8000</v>
+        <v>3700</v>
       </c>
       <c r="E59" s="3">
-        <v>13500</v>
+        <v>8700</v>
       </c>
       <c r="F59" s="3">
-        <v>7800</v>
+        <v>3100</v>
       </c>
       <c r="G59" s="3">
-        <v>11300</v>
+        <v>7000</v>
       </c>
       <c r="H59" s="3">
-        <v>13100</v>
+        <v>7300</v>
       </c>
       <c r="I59" s="3">
-        <v>10500</v>
+        <v>6700</v>
       </c>
       <c r="J59" s="3">
-        <v>12500</v>
+        <v>6400</v>
       </c>
       <c r="K59" s="3">
         <v>10200</v>
@@ -4654,25 +4654,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4736,26 +4736,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>2100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>2200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="H62" s="3">
-        <v>2900</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>2000</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>1600</v>
@@ -6215,25 +6215,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>400</v>
@@ -6826,26 +6826,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-200</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
-        <v>-100</v>
-      </c>
       <c r="J91" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
@@ -7189,26 +7189,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7604,26 +7604,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/UGRO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UGRO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>UGRO</t>
   </si>
@@ -656,378 +656,404 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>17900</v>
+      </c>
+      <c r="F8" s="3">
         <v>15500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>15000</v>
       </c>
-      <c r="F8" s="3">
-        <v>20900</v>
-      </c>
-      <c r="G8" s="3">
-        <v>18800</v>
-      </c>
       <c r="H8" s="3">
+        <v>19600</v>
+      </c>
+      <c r="I8" s="3">
+        <v>18500</v>
+      </c>
+      <c r="J8" s="3">
         <v>16800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>17300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>12400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>16300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>21100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>19000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>18300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>12800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>12000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>9200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>8400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>4000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>4300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>7100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>5600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>11500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>5800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>5400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>5300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>9300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>3400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F9" s="3">
         <v>12400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>13300</v>
       </c>
-      <c r="F9" s="3">
-        <v>18100</v>
-      </c>
-      <c r="G9" s="3">
-        <v>16000</v>
-      </c>
       <c r="H9" s="3">
+        <v>17200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>15900</v>
+      </c>
+      <c r="J9" s="3">
         <v>13900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>14100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>9800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>12800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>16200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>14000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>14000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>9900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>9400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>7500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>6700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>3100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>6000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>3700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>7900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>4200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>3900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>3700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>6500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F10" s="3">
         <v>3100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="L10" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M10" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N10" s="3">
+        <v>4900</v>
+      </c>
+      <c r="O10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="P10" s="3">
+        <v>4300</v>
+      </c>
+      <c r="Q10" s="3">
         <v>2900</v>
       </c>
-      <c r="G10" s="3">
-        <v>2900</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2800</v>
-      </c>
-      <c r="I10" s="3">
-        <v>3200</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="R10" s="3">
         <v>2600</v>
       </c>
-      <c r="K10" s="3">
-        <v>3500</v>
-      </c>
-      <c r="L10" s="3">
-        <v>4900</v>
-      </c>
-      <c r="M10" s="3">
-        <v>5000</v>
-      </c>
-      <c r="N10" s="3">
-        <v>4300</v>
-      </c>
-      <c r="O10" s="3">
-        <v>2900</v>
-      </c>
-      <c r="P10" s="3">
-        <v>2600</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>3600</v>
-      </c>
-      <c r="X10" s="3">
-        <v>1600</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>1500</v>
       </c>
       <c r="Z10" s="3">
         <v>1600</v>
       </c>
       <c r="AA10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AC10" s="3">
         <v>2800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,8 +1083,10 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1140,8 +1168,14 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,38 +1257,44 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>1500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>1400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>5000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1262,72 +1302,78 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-1000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>800</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>500</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E15" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F15" s="3">
         <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I15" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J15" s="3">
         <v>300</v>
@@ -1335,11 +1381,11 @@
       <c r="K15" s="3">
         <v>300</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>8</v>
+      <c r="L15" s="3">
+        <v>300</v>
+      </c>
+      <c r="M15" s="3">
+        <v>300</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>8</v>
@@ -1353,11 +1399,11 @@
       <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1389,8 +1435,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1469,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>20600</v>
+      </c>
+      <c r="F17" s="3">
         <v>17600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>19600</v>
       </c>
-      <c r="F17" s="3">
-        <v>24000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>22700</v>
-      </c>
       <c r="H17" s="3">
+        <v>23100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>22600</v>
+      </c>
+      <c r="J17" s="3">
         <v>21800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>20300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>16000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>18200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>21900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>19600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>18200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>11600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>12700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>9500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>8500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>5200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>5700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>8900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>7500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>14100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>7200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>7100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>6200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>10600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>4200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-4600</v>
       </c>
-      <c r="F18" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-3900</v>
-      </c>
       <c r="H18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-5000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-1900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-2600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,8 +1680,10 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1629,26 +1697,26 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1659,26 +1727,26 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1686,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="3">
         <v>0</v>
@@ -1697,115 +1765,127 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-4400</v>
       </c>
-      <c r="F21" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-3800</v>
-      </c>
       <c r="H21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="J21" s="3">
         <v>-4700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-1100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-1300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-1700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-1800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-2500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>300</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
@@ -1822,132 +1902,144 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>400</v>
-      </c>
-      <c r="R22" s="3">
-        <v>400</v>
       </c>
       <c r="S22" s="3">
         <v>400</v>
       </c>
       <c r="T22" s="3">
+        <v>400</v>
+      </c>
+      <c r="U22" s="3">
+        <v>400</v>
+      </c>
+      <c r="V22" s="3">
         <v>300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-4800</v>
       </c>
-      <c r="F23" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-5500</v>
-      </c>
       <c r="H23" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="J23" s="3">
         <v>-5200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-4200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-8700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-1700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-2800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-2900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-1300</v>
       </c>
       <c r="AB23" s="3">
         <v>-800</v>
       </c>
       <c r="AC23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1961,13 +2053,13 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-100</v>
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J24" s="3">
         <v>-100</v>
@@ -1979,10 +2071,10 @@
         <v>-100</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -2029,8 +2121,14 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2210,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-4700</v>
       </c>
-      <c r="F26" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-5400</v>
-      </c>
       <c r="H26" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="J26" s="3">
         <v>-5100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-4200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-8700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-1700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-2600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-2800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-2900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-1300</v>
       </c>
       <c r="AB26" s="3">
         <v>-800</v>
       </c>
       <c r="AC26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-4700</v>
       </c>
-      <c r="F27" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-5400</v>
-      </c>
       <c r="H27" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="J27" s="3">
         <v>-5100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-8700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-1700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-2600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-2900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-1300</v>
       </c>
       <c r="AB27" s="3">
         <v>-800</v>
       </c>
       <c r="AC27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2477,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2566,14 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2655,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,8 +2744,14 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2625,26 +2765,26 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2655,26 +2795,26 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -2682,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3">
         <v>0</v>
@@ -2693,91 +2833,103 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-4700</v>
       </c>
-      <c r="F33" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-5400</v>
-      </c>
       <c r="H33" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="J33" s="3">
         <v>-5100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-4200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-8700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-1700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-2600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-2900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-1300</v>
       </c>
       <c r="AB33" s="3">
         <v>-800</v>
       </c>
       <c r="AC33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +3011,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-4700</v>
       </c>
-      <c r="F35" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-5400</v>
-      </c>
       <c r="H35" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="J35" s="3">
         <v>-5100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-4200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-8700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-1700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-2600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-2900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-1300</v>
       </c>
       <c r="AB35" s="3">
         <v>-800</v>
       </c>
       <c r="AC35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3231,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,73 +3264,75 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>400</v>
+      </c>
+      <c r="F41" s="3">
         <v>700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>7300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>12000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>18600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>22800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>27100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>34600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>40500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>50400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>49900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>200</v>
-      </c>
-      <c r="S41" s="3">
-        <v>400</v>
-      </c>
-      <c r="T41" s="3">
-        <v>600</v>
       </c>
       <c r="U41" s="3">
         <v>400</v>
       </c>
       <c r="V41" s="3">
+        <v>600</v>
+      </c>
+      <c r="W41" s="3">
+        <v>400</v>
+      </c>
+      <c r="X41" s="3">
         <v>3500</v>
-      </c>
-      <c r="W41" s="3">
-        <v>1200</v>
-      </c>
-      <c r="X41" s="3">
-        <v>900</v>
       </c>
       <c r="Y41" s="3">
         <v>1200</v>
@@ -3167,16 +3341,22 @@
         <v>900</v>
       </c>
       <c r="AA41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AB41" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC41" s="3">
         <v>1000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>600</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,91 +3438,103 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>36200</v>
+      </c>
+      <c r="F43" s="3">
         <v>28900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>34700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>26700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>22400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>24900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>16000</v>
-      </c>
-      <c r="J43" s="3">
-        <v>13500</v>
-      </c>
-      <c r="K43" s="3">
-        <v>15400</v>
       </c>
       <c r="L43" s="3">
         <v>13500</v>
       </c>
       <c r="M43" s="3">
+        <v>15400</v>
+      </c>
+      <c r="N43" s="3">
+        <v>13500</v>
+      </c>
+      <c r="O43" s="3">
         <v>13100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>5800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>900</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3353,10 +3545,10 @@
         <v>200</v>
       </c>
       <c r="F44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H44" s="3">
         <v>300</v>
@@ -3368,49 +3560,49 @@
         <v>300</v>
       </c>
       <c r="K44" s="3">
+        <v>300</v>
+      </c>
+      <c r="L44" s="3">
+        <v>300</v>
+      </c>
+      <c r="M44" s="3">
         <v>400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>500</v>
-      </c>
-      <c r="N44" s="3">
-        <v>600</v>
-      </c>
-      <c r="O44" s="3">
-        <v>600</v>
       </c>
       <c r="P44" s="3">
         <v>600</v>
       </c>
       <c r="Q44" s="3">
+        <v>600</v>
+      </c>
+      <c r="R44" s="3">
+        <v>600</v>
+      </c>
+      <c r="S44" s="3">
         <v>500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>700</v>
-      </c>
-      <c r="V44" s="3">
-        <v>1000</v>
-      </c>
-      <c r="W44" s="3">
-        <v>1300</v>
       </c>
       <c r="X44" s="3">
         <v>1000</v>
       </c>
       <c r="Y44" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="Z44" s="3">
         <v>1000</v>
@@ -3419,179 +3611,197 @@
         <v>1200</v>
       </c>
       <c r="AB44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC44" s="3">
         <v>1200</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AE44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F45" s="3">
         <v>1900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>4900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>6100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>10100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>11200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>7800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>6200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>3500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>2700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>2100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>2500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1000</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>39400</v>
+      </c>
+      <c r="F46" s="3">
         <v>33200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>41000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>34800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>34500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>36900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>34600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>37300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>44800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>51000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>59500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>54700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>60300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>55200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>5200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>4600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>5300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>7000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>4800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>4900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>3900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>4300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>3700</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3604,32 +3814,32 @@
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H47" s="3">
-        <v>2600</v>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I47" s="3">
         <v>2600</v>
       </c>
       <c r="J47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="L47" s="3">
         <v>2500</v>
-      </c>
-      <c r="K47" s="3">
-        <v>4200</v>
-      </c>
-      <c r="L47" s="3">
-        <v>4200</v>
       </c>
       <c r="M47" s="3">
         <v>4200</v>
       </c>
       <c r="N47" s="3">
-        <v>1700</v>
+        <v>4200</v>
       </c>
       <c r="O47" s="3">
-        <v>1700</v>
+        <v>4200</v>
       </c>
       <c r="P47" s="3">
         <v>1700</v>
@@ -3644,170 +3854,182 @@
         <v>1700</v>
       </c>
       <c r="T47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V47" s="3">
         <v>1800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>2000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>1300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>1700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>1500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>1300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>1100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>500</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F48" s="3">
         <v>3200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1600</v>
-      </c>
-      <c r="L48" s="3">
-        <v>900</v>
-      </c>
-      <c r="M48" s="3">
-        <v>900</v>
       </c>
       <c r="N48" s="3">
         <v>900</v>
       </c>
       <c r="O48" s="3">
+        <v>900</v>
+      </c>
+      <c r="P48" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q48" s="3">
         <v>100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>200</v>
-      </c>
-      <c r="R48" s="3">
-        <v>300</v>
-      </c>
-      <c r="S48" s="3">
-        <v>300</v>
       </c>
       <c r="T48" s="3">
         <v>300</v>
       </c>
       <c r="U48" s="3">
+        <v>300</v>
+      </c>
+      <c r="V48" s="3">
+        <v>300</v>
+      </c>
+      <c r="W48" s="3">
         <v>400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>300</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F49" s="3">
         <v>19700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>20000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>20200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>20400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>20700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>21000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>16600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>15500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>9400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>9600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>10600</v>
-      </c>
-      <c r="O49" s="3">
-        <v>900</v>
-      </c>
-      <c r="P49" s="3">
-        <v>900</v>
       </c>
       <c r="Q49" s="3">
         <v>900</v>
       </c>
       <c r="R49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="S49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="T49" s="3">
         <v>1000</v>
@@ -3819,28 +4041,34 @@
         <v>1000</v>
       </c>
       <c r="W49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y49" s="3">
         <v>900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>900</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>100</v>
       </c>
       <c r="AA49" s="3">
         <v>100</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4150,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,8 +4239,14 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4031,51 +4271,51 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>8</v>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3">
-        <v>100</v>
-      </c>
-      <c r="P52" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
+      <c r="R52" s="3">
+        <v>100</v>
+      </c>
+      <c r="S52" s="3">
+        <v>100</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
         <v>100</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
       <c r="Z52" s="3">
         <v>0</v>
       </c>
@@ -4083,13 +4323,19 @@
         <v>0</v>
       </c>
       <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
         <v>100</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4417,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>49200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>55000</v>
+      </c>
+      <c r="F54" s="3">
         <v>56100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>64400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>58600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>61300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>64100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>62100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>58400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>66100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>65500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>74200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>68000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>63100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>58000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>8200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>7600</v>
-      </c>
-      <c r="S54" s="3">
-        <v>7400</v>
-      </c>
-      <c r="T54" s="3">
-        <v>8500</v>
       </c>
       <c r="U54" s="3">
         <v>7400</v>
       </c>
       <c r="V54" s="3">
+        <v>8500</v>
+      </c>
+      <c r="W54" s="3">
+        <v>7400</v>
+      </c>
+      <c r="X54" s="3">
         <v>10100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>8100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>8000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>5700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>5500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>5200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>4600</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4543,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,370 +4576,396 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>31700</v>
+      </c>
+      <c r="F57" s="3">
         <v>25000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>25400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>22200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>18600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>14900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>10000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>6500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>7900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>7900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>6100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>3800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>3700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>3300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>3400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>900</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F58" s="3">
         <v>3200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>3500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>1000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>7100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>6200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>6000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>3800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>4200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>3200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>3500</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>500</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>500</v>
       </c>
       <c r="AB58" s="3">
         <v>500</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F59" s="3">
         <v>3700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>8700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>7000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>7300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>6700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>6400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>10200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>12100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>18900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>15400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>11300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>6200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>6800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>6000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>5400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>5400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>4800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>5700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>3900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>4400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>4500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>6400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>5700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>5100</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>45700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>48000</v>
+      </c>
+      <c r="F60" s="3">
         <v>35500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>42100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>31900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>31800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>30900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>24300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>19000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>18200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>20100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>25000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>18200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>13600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>9500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>14500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>9400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>13000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>14000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>12300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>13500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>10300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>11200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>9600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>8100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>7400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>6400</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F61" s="3">
         <v>1300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4693,35 +4979,35 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3">
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="S61" s="3">
         <v>1000</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="U61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>1800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>200</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -4731,8 +5017,14 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4757,35 +5049,35 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>1600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U62" s="3">
         <v>100</v>
@@ -4794,16 +5086,16 @@
         <v>100</v>
       </c>
       <c r="W62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
+        <v>100</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>8</v>
@@ -4814,8 +5106,14 @@
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5195,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5284,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5373,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>49200</v>
+      </c>
+      <c r="F66" s="3">
         <v>37500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>44300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>34500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>34600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>33800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>27300</v>
-      </c>
-      <c r="J66" s="3">
-        <v>20900</v>
-      </c>
-      <c r="K66" s="3">
-        <v>19800</v>
       </c>
       <c r="L66" s="3">
         <v>20900</v>
       </c>
       <c r="M66" s="3">
+        <v>19800</v>
+      </c>
+      <c r="N66" s="3">
+        <v>20900</v>
+      </c>
+      <c r="O66" s="3">
         <v>26000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>19200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>13600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>9500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>15600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>14300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>14000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>14100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>12400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>15400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>11100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>11500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>9600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>8100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>7400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>6400</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5499,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5584,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5673,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5762,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5851,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-75600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-71800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-58900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-56800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-52100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-48700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-43300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-38100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-33900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-25300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-23500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-22800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-22200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-22300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-22000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-20900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-20200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-18600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-16900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-14300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-11400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +6029,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +6118,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6207,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F76" s="3">
         <v>18600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>20100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>24200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>26700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>30300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>34700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>37500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>46300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>44600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>48200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>48800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>49500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>48600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-7400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-6700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-6600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-5600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-5000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-5300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-3000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6385,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-4700</v>
       </c>
-      <c r="F81" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-5400</v>
-      </c>
       <c r="H81" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="J81" s="3">
         <v>-5100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-4200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-8700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-1700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-2600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-2900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-1300</v>
       </c>
       <c r="AB81" s="3">
         <v>-800</v>
       </c>
       <c r="AC81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AD81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,25 +6605,27 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>300</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
-      </c>
-      <c r="E83" s="3">
-        <v>100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
@@ -6236,22 +6634,22 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
         <v>400</v>
-      </c>
-      <c r="L83" s="3">
-        <v>200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>200</v>
       </c>
       <c r="N83" s="3">
         <v>200</v>
       </c>
       <c r="O83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
@@ -6278,22 +6676,28 @@
         <v>100</v>
       </c>
       <c r="Y83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
         <v>100</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6779,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6868,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6957,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +7046,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +7135,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F89" s="3">
         <v>300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-4700</v>
       </c>
-      <c r="F89" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="G89" s="3">
-        <v>3600</v>
-      </c>
       <c r="H89" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="I89" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J89" s="3">
         <v>-4300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-3600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-4100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-3700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-2400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-1600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,91 +7261,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
+      <c r="D91" s="3">
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>100</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-100</v>
       </c>
       <c r="AC91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7435,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7524,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>2100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-3100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-2600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-5700</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7650,10 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7210,11 +7678,11 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7267,8 +7735,14 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7824,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7913,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,91 +8002,103 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-2300</v>
-      </c>
       <c r="H100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-3800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-3200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>49400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>1200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>2000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>1100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>2200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>3000</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7625,11 +8123,11 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7682,87 +8180,99 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-3700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-3800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-4700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-6600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-4200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-4300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-7500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-5900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-9900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>49700</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-3100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>2300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UGRO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UGRO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
   <si>
     <t>UGRO</t>
   </si>
@@ -797,7 +797,7 @@
         <v>17900</v>
       </c>
       <c r="F8" s="3">
-        <v>15500</v>
+        <v>15400</v>
       </c>
       <c r="G8" s="3">
         <v>15000</v>
@@ -898,7 +898,7 @@
         <v>15900</v>
       </c>
       <c r="J9" s="3">
-        <v>13900</v>
+        <v>13700</v>
       </c>
       <c r="K9" s="3">
         <v>14100</v>
@@ -975,7 +975,7 @@
         <v>2400</v>
       </c>
       <c r="F10" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="G10" s="3">
         <v>1700</v>
@@ -987,7 +987,7 @@
         <v>2500</v>
       </c>
       <c r="J10" s="3">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="K10" s="3">
         <v>3200</v>
@@ -1364,7 +1364,7 @@
         <v>400</v>
       </c>
       <c r="F15" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3">
         <v>200</v>
@@ -1376,7 +1376,7 @@
         <v>400</v>
       </c>
       <c r="J15" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K15" s="3">
         <v>300</v>
@@ -1483,7 +1483,7 @@
         <v>20600</v>
       </c>
       <c r="F17" s="3">
-        <v>17600</v>
+        <v>17900</v>
       </c>
       <c r="G17" s="3">
         <v>19600</v>
@@ -1572,7 +1572,7 @@
         <v>-2700</v>
       </c>
       <c r="F18" s="3">
-        <v>-2100</v>
+        <v>-2500</v>
       </c>
       <c r="G18" s="3">
         <v>-4600</v>
@@ -1584,7 +1584,7 @@
         <v>-4100</v>
       </c>
       <c r="J18" s="3">
-        <v>-5000</v>
+        <v>-5100</v>
       </c>
       <c r="K18" s="3">
         <v>-2900</v>
@@ -1783,7 +1783,7 @@
         <v>-2300</v>
       </c>
       <c r="F21" s="3">
-        <v>-1900</v>
+        <v>-2100</v>
       </c>
       <c r="G21" s="3">
         <v>-4400</v>
@@ -1961,7 +1961,7 @@
         <v>-3000</v>
       </c>
       <c r="F23" s="3">
-        <v>-2200</v>
+        <v>-2600</v>
       </c>
       <c r="G23" s="3">
         <v>-4800</v>
@@ -1973,7 +1973,7 @@
         <v>-5800</v>
       </c>
       <c r="J23" s="3">
-        <v>-5200</v>
+        <v>-5300</v>
       </c>
       <c r="K23" s="3">
         <v>-4200</v>
@@ -2061,8 +2061,8 @@
       <c r="I24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="3">
-        <v>-100</v>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K24" s="3">
         <v>-100</v>
@@ -2228,7 +2228,7 @@
         <v>-3000</v>
       </c>
       <c r="F26" s="3">
-        <v>-2100</v>
+        <v>-2600</v>
       </c>
       <c r="G26" s="3">
         <v>-4700</v>
@@ -2240,7 +2240,7 @@
         <v>-5800</v>
       </c>
       <c r="J26" s="3">
-        <v>-5100</v>
+        <v>-5300</v>
       </c>
       <c r="K26" s="3">
         <v>-4200</v>
@@ -2317,7 +2317,7 @@
         <v>-3000</v>
       </c>
       <c r="F27" s="3">
-        <v>-2100</v>
+        <v>-2600</v>
       </c>
       <c r="G27" s="3">
         <v>-4700</v>
@@ -2329,7 +2329,7 @@
         <v>-5800</v>
       </c>
       <c r="J27" s="3">
-        <v>-5100</v>
+        <v>-5300</v>
       </c>
       <c r="K27" s="3">
         <v>-4200</v>
@@ -2851,7 +2851,7 @@
         <v>-3000</v>
       </c>
       <c r="F33" s="3">
-        <v>-2100</v>
+        <v>-2600</v>
       </c>
       <c r="G33" s="3">
         <v>-4700</v>
@@ -2863,7 +2863,7 @@
         <v>-5800</v>
       </c>
       <c r="J33" s="3">
-        <v>-5100</v>
+        <v>-5300</v>
       </c>
       <c r="K33" s="3">
         <v>-4200</v>
@@ -3029,7 +3029,7 @@
         <v>-3000</v>
       </c>
       <c r="F35" s="3">
-        <v>-2100</v>
+        <v>-2600</v>
       </c>
       <c r="G35" s="3">
         <v>-4700</v>
@@ -3041,7 +3041,7 @@
         <v>-5800</v>
       </c>
       <c r="J35" s="3">
-        <v>-5100</v>
+        <v>-5300</v>
       </c>
       <c r="K35" s="3">
         <v>-4200</v>
@@ -3278,7 +3278,7 @@
         <v>400</v>
       </c>
       <c r="F41" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G41" s="3">
         <v>1100</v>
@@ -3456,7 +3456,7 @@
         <v>36200</v>
       </c>
       <c r="F43" s="3">
-        <v>28900</v>
+        <v>26400</v>
       </c>
       <c r="G43" s="3">
         <v>34700</v>
@@ -3634,7 +3634,7 @@
         <v>1700</v>
       </c>
       <c r="F45" s="3">
-        <v>1900</v>
+        <v>1000</v>
       </c>
       <c r="G45" s="3">
         <v>3600</v>
@@ -3723,7 +3723,7 @@
         <v>39400</v>
       </c>
       <c r="F46" s="3">
-        <v>33200</v>
+        <v>29600</v>
       </c>
       <c r="G46" s="3">
         <v>41000</v>
@@ -3990,7 +3990,7 @@
         <v>12800</v>
       </c>
       <c r="F49" s="3">
-        <v>19700</v>
+        <v>12900</v>
       </c>
       <c r="G49" s="3">
         <v>20000</v>
@@ -4435,7 +4435,7 @@
         <v>55000</v>
       </c>
       <c r="F54" s="3">
-        <v>56100</v>
+        <v>45700</v>
       </c>
       <c r="G54" s="3">
         <v>64400</v>
@@ -4590,7 +4590,7 @@
         <v>31700</v>
       </c>
       <c r="F57" s="3">
-        <v>25000</v>
+        <v>23800</v>
       </c>
       <c r="G57" s="3">
         <v>25400</v>
@@ -4768,7 +4768,7 @@
         <v>6300</v>
       </c>
       <c r="F59" s="3">
-        <v>3700</v>
+        <v>4200</v>
       </c>
       <c r="G59" s="3">
         <v>8700</v>
@@ -4857,7 +4857,7 @@
         <v>48000</v>
       </c>
       <c r="F60" s="3">
-        <v>35500</v>
+        <v>36300</v>
       </c>
       <c r="G60" s="3">
         <v>42100</v>
@@ -5869,7 +5869,7 @@
         <v>-71800</v>
       </c>
       <c r="F72" s="3">
-        <v>-58900</v>
+        <v>-68800</v>
       </c>
       <c r="G72" s="3">
         <v>-56800</v>
@@ -6225,7 +6225,7 @@
         <v>5800</v>
       </c>
       <c r="F76" s="3">
-        <v>18600</v>
+        <v>8200</v>
       </c>
       <c r="G76" s="3">
         <v>20100</v>
@@ -6497,7 +6497,7 @@
         <v>-3000</v>
       </c>
       <c r="F81" s="3">
-        <v>-2100</v>
+        <v>-2600</v>
       </c>
       <c r="G81" s="3">
         <v>-4700</v>
@@ -6509,7 +6509,7 @@
         <v>-5800</v>
       </c>
       <c r="J81" s="3">
-        <v>-5100</v>
+        <v>-5300</v>
       </c>
       <c r="K81" s="3">
         <v>-4200</v>
@@ -6619,7 +6619,7 @@
         <v>300</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -7153,7 +7153,7 @@
         <v>-2100</v>
       </c>
       <c r="F89" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="G89" s="3">
         <v>-4700</v>
@@ -7165,7 +7165,7 @@
         <v>3000</v>
       </c>
       <c r="J89" s="3">
-        <v>-4300</v>
+        <v>-3400</v>
       </c>
       <c r="K89" s="3">
         <v>-3600</v>
@@ -8020,7 +8020,7 @@
         <v>1900</v>
       </c>
       <c r="F100" s="3">
-        <v>-800</v>
+        <v>-1100</v>
       </c>
       <c r="G100" s="3">
         <v>1200</v>
@@ -8032,7 +8032,7 @@
         <v>-1700</v>
       </c>
       <c r="J100" s="3">
-        <v>-300</v>
+        <v>-1200</v>
       </c>
       <c r="K100" s="3">
         <v>-1500</v>

--- a/AAII_Financials/Quarterly/UGRO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UGRO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
   <si>
     <t>UGRO</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
@@ -683,377 +683,428 @@
     <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="H7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="V7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="X7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="Y7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Z7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="AA7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AB7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AC7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AD7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AE7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AF7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AG7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AH7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AI7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>9900</v>
-      </c>
-      <c r="E8" s="3">
-        <v>17900</v>
+        <v>2400</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F8" s="3">
+        <v>9500</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3">
         <v>15400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="K8" s="3">
         <v>15000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="L8" s="3">
         <v>19600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="M8" s="3">
         <v>18500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="N8" s="3">
         <v>16800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="O8" s="3">
         <v>17300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="P8" s="3">
         <v>12400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="Q8" s="3">
         <v>16300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="R8" s="3">
         <v>21100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="S8" s="3">
         <v>19000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="T8" s="3">
         <v>18300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="U8" s="3">
         <v>12800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="V8" s="3">
         <v>12000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="W8" s="3">
         <v>9200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="X8" s="3">
         <v>8400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="Y8" s="3">
         <v>4000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Z8" s="3">
         <v>4300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="AA8" s="3">
         <v>7100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AB8" s="3">
         <v>5600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AC8" s="3">
         <v>11500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AD8" s="3">
         <v>5800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AE8" s="3">
         <v>5400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AF8" s="3">
         <v>5300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AG8" s="3">
         <v>9300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AH8" s="3">
         <v>3400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AI8" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>8600</v>
-      </c>
-      <c r="E9" s="3">
-        <v>15500</v>
+        <v>2600</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F9" s="3">
+        <v>8900</v>
+      </c>
+      <c r="G9" s="3">
+        <v>600</v>
+      </c>
+      <c r="H9" s="3">
+        <v>7300</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3">
         <v>12400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="K9" s="3">
         <v>13300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="L9" s="3">
         <v>17200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="M9" s="3">
         <v>15900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="N9" s="3">
         <v>13700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="O9" s="3">
         <v>14100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="P9" s="3">
         <v>9800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="Q9" s="3">
         <v>12800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="R9" s="3">
         <v>16200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="S9" s="3">
         <v>14000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="T9" s="3">
         <v>14000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="U9" s="3">
         <v>9900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="V9" s="3">
         <v>9400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="W9" s="3">
         <v>7500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="X9" s="3">
         <v>6700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="Y9" s="3">
         <v>2800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Z9" s="3">
         <v>3100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="AA9" s="3">
         <v>6000</v>
-      </c>
-      <c r="X9" s="3">
-        <v>3700</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>7900</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>4200</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>3900</v>
       </c>
       <c r="AB9" s="3">
         <v>3700</v>
       </c>
       <c r="AC9" s="3">
+        <v>7900</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AG9" s="3">
         <v>6500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AH9" s="3">
         <v>2400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AI9" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1300</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2400</v>
+        <v>-200</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F10" s="3">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="G10" s="3">
-        <v>1700</v>
+        <v>-3800</v>
       </c>
       <c r="H10" s="3">
-        <v>2400</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2500</v>
+        <v>700</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J10" s="3">
         <v>3000</v>
       </c>
       <c r="K10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L10" s="3">
+        <v>2400</v>
+      </c>
+      <c r="M10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O10" s="3">
         <v>3200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="P10" s="3">
         <v>2600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="Q10" s="3">
         <v>3500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="R10" s="3">
         <v>4900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="S10" s="3">
         <v>5000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="T10" s="3">
         <v>4300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="U10" s="3">
         <v>2900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="V10" s="3">
         <v>2600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="W10" s="3">
         <v>1700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="X10" s="3">
         <v>1700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="Y10" s="3">
         <v>1200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Z10" s="3">
         <v>1200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="AA10" s="3">
         <v>1100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AB10" s="3">
         <v>1900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AC10" s="3">
         <v>3600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AD10" s="3">
         <v>1600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AE10" s="3">
         <v>1500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AF10" s="3">
         <v>1600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AG10" s="3">
         <v>2800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AH10" s="3">
         <v>1000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AI10" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1085,8 +1136,12 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1174,8 +1229,20 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,13 +1330,25 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>2300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1278,73 +1357,73 @@
         <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
+        <v>11500</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="M14" s="3">
         <v>1500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="O14" s="3">
         <v>1400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="P14" s="3">
         <v>5000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-1000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="V14" s="3">
         <v>800</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>500</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1352,25 +1431,37 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
         <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
         <v>400</v>
@@ -1379,43 +1470,43 @@
         <v>400</v>
       </c>
       <c r="K15" s="3">
+        <v>200</v>
+      </c>
+      <c r="L15" s="3">
+        <v>400</v>
+      </c>
+      <c r="M15" s="3">
+        <v>400</v>
+      </c>
+      <c r="N15" s="3">
+        <v>400</v>
+      </c>
+      <c r="O15" s="3">
         <v>300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="P15" s="3">
         <v>300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="Q15" s="3">
         <v>300</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
-      </c>
-      <c r="U15" s="3">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
-      </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1441,8 +1532,20 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1574,214 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13400</v>
-      </c>
-      <c r="E17" s="3">
-        <v>20600</v>
+        <v>4600</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F17" s="3">
+        <v>13600</v>
+      </c>
+      <c r="G17" s="3">
+        <v>12400</v>
+      </c>
+      <c r="H17" s="3">
+        <v>11200</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3">
         <v>17900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="K17" s="3">
         <v>19600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="L17" s="3">
         <v>23100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="M17" s="3">
         <v>22600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="N17" s="3">
         <v>21800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="O17" s="3">
         <v>20300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="P17" s="3">
         <v>16000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="Q17" s="3">
         <v>18200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="R17" s="3">
         <v>21900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="S17" s="3">
         <v>19600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="T17" s="3">
         <v>18200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="U17" s="3">
         <v>11600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="V17" s="3">
         <v>12700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="W17" s="3">
         <v>9500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="X17" s="3">
         <v>8500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Y17" s="3">
         <v>5200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <v>5700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="AA17" s="3">
         <v>8900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AB17" s="3">
         <v>7500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AC17" s="3">
         <v>14100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AD17" s="3">
         <v>7200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AE17" s="3">
         <v>7100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AF17" s="3">
         <v>6200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AG17" s="3">
         <v>10600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AH17" s="3">
         <v>4200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AI17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="L18" s="3">
         <v>-3500</v>
       </c>
-      <c r="E18" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="M18" s="3">
         <v>-4100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="N18" s="3">
         <v>-5100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="O18" s="3">
         <v>-2900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="P18" s="3">
         <v>-3600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="Q18" s="3">
         <v>-1900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="R18" s="3">
         <v>-800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="S18" s="3">
         <v>-600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="T18" s="3">
         <v>100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="U18" s="3">
         <v>1200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="V18" s="3">
         <v>-700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="W18" s="3">
         <v>-300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="Y18" s="3">
         <v>-1200</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-2600</v>
       </c>
       <c r="Z18" s="3">
         <v>-1400</v>
       </c>
       <c r="AA18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AF18" s="3">
         <v>-900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AG18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AH18" s="3">
         <v>-800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AI18" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,28 +1813,32 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
-      <c r="I20" s="3">
-        <v>100</v>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1712,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
@@ -1724,123 +1859,135 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="X20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="L21" s="3">
         <v>-3200</v>
       </c>
-      <c r="E21" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="M21" s="3">
         <v>-3900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="N21" s="3">
         <v>-4700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="O21" s="3">
         <v>-2600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="P21" s="3">
         <v>-3500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="Q21" s="3">
         <v>-1400</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="P21" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>1300</v>
       </c>
       <c r="R21" s="3">
         <v>-600</v>
       </c>
       <c r="S21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="T21" s="3">
+        <v>200</v>
+      </c>
+      <c r="U21" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V21" s="3">
         <v>-600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="W21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X21" s="3">
         <v>-200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="Y21" s="3">
         <v>-1100</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-2500</v>
       </c>
       <c r="Z21" s="3">
         <v>-1300</v>
@@ -1849,45 +1996,57 @@
         <v>-1700</v>
       </c>
       <c r="AB21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AG21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AH21" s="3">
         <v>-700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AI21" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3">
+        <v>500</v>
+      </c>
+      <c r="G22" s="3">
+        <v>400</v>
+      </c>
+      <c r="H22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3">
-        <v>300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>100</v>
-      </c>
-      <c r="G22" s="3">
-        <v>100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1896,7 +2055,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1908,152 +2067,176 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>1000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="W22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="X22" s="3">
         <v>400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="Y22" s="3">
         <v>400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="Z22" s="3">
         <v>300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="AA22" s="3">
         <v>900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="AB22" s="3">
         <v>900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AC22" s="3">
         <v>200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AD22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AE22" s="3">
         <v>100</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="L23" s="3">
         <v>-3800</v>
       </c>
-      <c r="E23" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="M23" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="O23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T23" s="3">
+        <v>100</v>
+      </c>
+      <c r="U23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="W23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-2600</v>
       </c>
-      <c r="G23" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="AB23" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="AF23" s="3">
         <v>-800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="AG23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AI23" s="3">
         <v>-600</v>
       </c>
-      <c r="P23" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>1300</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-700</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>8</v>
@@ -2061,33 +2244,33 @@
       <c r="I24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>8</v>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -2127,8 +2310,20 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2411,222 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L26" s="3">
         <v>-3800</v>
       </c>
-      <c r="E26" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="M26" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="S26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T26" s="3">
+        <v>100</v>
+      </c>
+      <c r="U26" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="W26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-2600</v>
       </c>
-      <c r="G26" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-700</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="AB26" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AI26" s="3">
         <v>-600</v>
       </c>
-      <c r="P26" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>1300</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-700</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-3000</v>
+        <v>-4800</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F27" s="3">
-        <v>-2600</v>
+        <v>-4000</v>
       </c>
       <c r="G27" s="3">
-        <v>-4700</v>
+        <v>-27200</v>
       </c>
       <c r="H27" s="3">
         <v>-3800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="M27" s="3">
         <v>-5800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="N27" s="3">
         <v>-5300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="O27" s="3">
         <v>-4200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="P27" s="3">
         <v>-8700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="Q27" s="3">
         <v>-1700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="R27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="S27" s="3">
         <v>-600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="T27" s="3">
         <v>100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="U27" s="3">
         <v>1300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="V27" s="3">
         <v>-1600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="W27" s="3">
         <v>-1100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="X27" s="3">
         <v>-700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="Y27" s="3">
         <v>-1600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Z27" s="3">
         <v>-1700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="AA27" s="3">
         <v>-2600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="AB27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AC27" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AD27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AE27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AF27" s="3">
         <v>-800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AG27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AH27" s="3">
         <v>-800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AI27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,13 +2714,25 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2501,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -2572,8 +2815,20 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2916,20 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,28 +3017,40 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
-      <c r="I32" s="3">
-        <v>-100</v>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2780,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
@@ -2792,144 +3071,168 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="X32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-3000</v>
+        <v>-4800</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F33" s="3">
-        <v>-2600</v>
+        <v>-4000</v>
       </c>
       <c r="G33" s="3">
-        <v>-4700</v>
+        <v>-27200</v>
       </c>
       <c r="H33" s="3">
         <v>-3800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="M33" s="3">
         <v>-5800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="N33" s="3">
         <v>-5300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="O33" s="3">
         <v>-4200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="P33" s="3">
         <v>-8700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="Q33" s="3">
         <v>-1700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="R33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="S33" s="3">
         <v>-600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="T33" s="3">
         <v>100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="U33" s="3">
         <v>1300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="V33" s="3">
         <v>-1600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="W33" s="3">
         <v>-1100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="X33" s="3">
         <v>-700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="Y33" s="3">
         <v>-1600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Z33" s="3">
         <v>-1700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="AA33" s="3">
         <v>-2600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="AB33" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AC33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AD33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AE33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AF33" s="3">
         <v>-800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AG33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AH33" s="3">
         <v>-800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AI33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3320,227 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-3000</v>
+        <v>-4800</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F35" s="3">
-        <v>-2600</v>
+        <v>-4000</v>
       </c>
       <c r="G35" s="3">
-        <v>-4700</v>
+        <v>-27200</v>
       </c>
       <c r="H35" s="3">
         <v>-3800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="M35" s="3">
         <v>-5800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="N35" s="3">
         <v>-5300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="O35" s="3">
         <v>-4200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="P35" s="3">
         <v>-8700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="Q35" s="3">
         <v>-1700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="R35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="S35" s="3">
         <v>-600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="T35" s="3">
         <v>100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="U35" s="3">
         <v>1300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="V35" s="3">
         <v>-1600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="W35" s="3">
         <v>-1100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="X35" s="3">
         <v>-700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="Y35" s="3">
         <v>-1600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Z35" s="3">
         <v>-1700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="AA35" s="3">
         <v>-2600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="AB35" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AC35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AD35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AE35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AF35" s="3">
         <v>-800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AG35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AH35" s="3">
         <v>-800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AI35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="H38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="V38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="X38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="Y38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Z38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="AA38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="AB38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AC38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AD38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AE38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AF38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AG38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AH38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AI38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3572,12 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,97 +3609,113 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>700</v>
+      </c>
+      <c r="F41" s="3">
+        <v>700</v>
+      </c>
+      <c r="G41" s="3">
+        <v>800</v>
+      </c>
+      <c r="H41" s="3">
         <v>1100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="I41" s="3">
         <v>400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="J41" s="3">
         <v>600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="K41" s="3">
         <v>1100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>4800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>8600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>7300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>12000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>18600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>22800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="R41" s="3">
         <v>27100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="S41" s="3">
         <v>34600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="T41" s="3">
         <v>40500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="U41" s="3">
         <v>50400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="V41" s="3">
         <v>49900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="W41" s="3">
         <v>200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="X41" s="3">
         <v>200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="Y41" s="3">
         <v>400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Z41" s="3">
         <v>600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="AA41" s="3">
         <v>400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="AB41" s="3">
         <v>3500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AC41" s="3">
         <v>1200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AD41" s="3">
         <v>900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AE41" s="3">
         <v>1200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AF41" s="3">
         <v>900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AG41" s="3">
         <v>1000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AH41" s="3">
         <v>600</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3444,97 +3803,121 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F43" s="3">
+        <v>9200</v>
+      </c>
+      <c r="G43" s="3">
+        <v>12500</v>
+      </c>
+      <c r="H43" s="3">
         <v>28500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="I43" s="3">
         <v>36200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="J43" s="3">
         <v>26400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="K43" s="3">
         <v>34700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>26700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>22400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>24900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>16000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>13500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>15400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="R43" s="3">
         <v>13500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="S43" s="3">
         <v>13100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="T43" s="3">
         <v>5800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="U43" s="3">
         <v>3000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="V43" s="3">
         <v>800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="W43" s="3">
         <v>1000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="X43" s="3">
         <v>900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="Y43" s="3">
         <v>900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Z43" s="3">
         <v>1400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="AA43" s="3">
         <v>1600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="AB43" s="3">
         <v>1700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AC43" s="3">
         <v>1300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AD43" s="3">
         <v>1100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AE43" s="3">
         <v>600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AF43" s="3">
         <v>1000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AG43" s="3">
         <v>900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AH43" s="3">
         <v>900</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3551,257 +3934,293 @@
         <v>200</v>
       </c>
       <c r="H44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L44" s="3">
         <v>300</v>
       </c>
       <c r="M44" s="3">
+        <v>300</v>
+      </c>
+      <c r="N44" s="3">
+        <v>300</v>
+      </c>
+      <c r="O44" s="3">
+        <v>300</v>
+      </c>
+      <c r="P44" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q44" s="3">
         <v>400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="R44" s="3">
         <v>400</v>
-      </c>
-      <c r="O44" s="3">
-        <v>500</v>
-      </c>
-      <c r="P44" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>600</v>
-      </c>
-      <c r="R44" s="3">
-        <v>600</v>
       </c>
       <c r="S44" s="3">
         <v>500</v>
       </c>
       <c r="T44" s="3">
+        <v>600</v>
+      </c>
+      <c r="U44" s="3">
+        <v>600</v>
+      </c>
+      <c r="V44" s="3">
+        <v>600</v>
+      </c>
+      <c r="W44" s="3">
+        <v>500</v>
+      </c>
+      <c r="X44" s="3">
         <v>800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="Y44" s="3">
         <v>1000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="Z44" s="3">
         <v>900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="AA44" s="3">
         <v>700</v>
-      </c>
-      <c r="X44" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>1200</v>
       </c>
       <c r="AB44" s="3">
         <v>1000</v>
       </c>
       <c r="AC44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AD44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE44" s="3">
         <v>1200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG44" s="3">
         <v>1200</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AI44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H45" s="3">
         <v>3300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="I45" s="3">
         <v>1700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="K45" s="3">
         <v>3600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>1600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="M45" s="3">
         <v>2400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="N45" s="3">
         <v>3300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>4900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="P45" s="3">
         <v>3400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
         <v>6100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="R45" s="3">
         <v>10100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="S45" s="3">
         <v>11200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="T45" s="3">
         <v>7800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="U45" s="3">
         <v>6200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="V45" s="3">
         <v>3900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="W45" s="3">
         <v>3500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="X45" s="3">
         <v>2700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="Y45" s="3">
         <v>2100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="Z45" s="3">
         <v>2500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="AA45" s="3">
         <v>1300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="AB45" s="3">
         <v>800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AC45" s="3">
         <v>1100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AD45" s="3">
         <v>1900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AE45" s="3">
         <v>900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AF45" s="3">
         <v>1100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AG45" s="3">
         <v>1200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AH45" s="3">
         <v>1000</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F46" s="3">
+        <v>13400</v>
+      </c>
+      <c r="G46" s="3">
+        <v>15800</v>
+      </c>
+      <c r="H46" s="3">
         <v>33800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="I46" s="3">
         <v>39400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="J46" s="3">
         <v>29600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="K46" s="3">
         <v>41000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>34800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>34500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>36900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>34600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>37300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>44800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="R46" s="3">
         <v>51000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="S46" s="3">
         <v>59500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="T46" s="3">
         <v>54700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="U46" s="3">
         <v>60300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="V46" s="3">
         <v>55200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="W46" s="3">
         <v>5200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="X46" s="3">
         <v>4600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="Y46" s="3">
         <v>4400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Z46" s="3">
         <v>5300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="AA46" s="3">
         <v>4000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="AB46" s="3">
         <v>7000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AC46" s="3">
         <v>4800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AD46" s="3">
         <v>4900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AE46" s="3">
         <v>3900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AF46" s="3">
         <v>3800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AG46" s="3">
         <v>4300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AH46" s="3">
         <v>3700</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3820,38 +4239,38 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>2600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="N47" s="3">
         <v>2600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>2600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>2500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="Q47" s="3">
         <v>4200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="R47" s="3">
         <v>4200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="S47" s="3">
         <v>4200</v>
-      </c>
-      <c r="P47" s="3">
-        <v>1700</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>1700</v>
-      </c>
-      <c r="R47" s="3">
-        <v>1700</v>
-      </c>
-      <c r="S47" s="3">
-        <v>1700</v>
       </c>
       <c r="T47" s="3">
         <v>1700</v>
@@ -3860,215 +4279,251 @@
         <v>1700</v>
       </c>
       <c r="V47" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="W47" s="3">
-        <v>2000</v>
+        <v>1700</v>
       </c>
       <c r="X47" s="3">
-        <v>1300</v>
+        <v>1700</v>
       </c>
       <c r="Y47" s="3">
         <v>1700</v>
       </c>
       <c r="Z47" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AD47" s="3">
         <v>1500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AE47" s="3">
         <v>1300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AF47" s="3">
         <v>1100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AG47" s="3">
         <v>500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AH47" s="3">
         <v>500</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H48" s="3">
         <v>2900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="I48" s="3">
         <v>2900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="J48" s="3">
         <v>3200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="K48" s="3">
         <v>3500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>3700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="M48" s="3">
         <v>3700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>3900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>3900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>2000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>1600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="R48" s="3">
         <v>900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="S48" s="3">
         <v>900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="T48" s="3">
         <v>900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="U48" s="3">
         <v>100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="V48" s="3">
         <v>200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="W48" s="3">
         <v>200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="X48" s="3">
         <v>300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="Y48" s="3">
         <v>300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Z48" s="3">
         <v>300</v>
-      </c>
-      <c r="W48" s="3">
-        <v>400</v>
-      </c>
-      <c r="X48" s="3">
-        <v>900</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>500</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>600</v>
       </c>
       <c r="AA48" s="3">
         <v>400</v>
       </c>
       <c r="AB48" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE48" s="3">
         <v>400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AF48" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG48" s="3">
         <v>300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AH48" s="3">
         <v>300</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G49" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H49" s="3">
         <v>12600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="I49" s="3">
         <v>12800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="J49" s="3">
         <v>12900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="K49" s="3">
         <v>20000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="L49" s="3">
         <v>20200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="M49" s="3">
         <v>20400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="N49" s="3">
         <v>20700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="O49" s="3">
         <v>21000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="P49" s="3">
         <v>16600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="Q49" s="3">
         <v>15500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="R49" s="3">
         <v>9400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="S49" s="3">
         <v>9600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="T49" s="3">
         <v>10600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="U49" s="3">
         <v>900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="V49" s="3">
         <v>900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="W49" s="3">
         <v>900</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="W49" s="3">
-        <v>1000</v>
       </c>
       <c r="X49" s="3">
         <v>1000</v>
       </c>
       <c r="Y49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC49" s="3">
         <v>900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AD49" s="3">
         <v>900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AE49" s="3">
         <v>100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AF49" s="3">
         <v>100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AG49" s="3">
         <v>100</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4611,20 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,8 +4712,20 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4277,65 +4756,77 @@
       <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="W52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
         <v>100</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>0</v>
-      </c>
       <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
         <v>100</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,97 +4914,121 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F54" s="3">
+        <v>16100</v>
+      </c>
+      <c r="G54" s="3">
+        <v>19500</v>
+      </c>
+      <c r="H54" s="3">
         <v>49200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="I54" s="3">
         <v>55000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="J54" s="3">
         <v>45700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="K54" s="3">
         <v>64400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>58600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>61300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>64100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>62100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>58400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>66100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="R54" s="3">
         <v>65500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="S54" s="3">
         <v>74200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="T54" s="3">
         <v>68000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="U54" s="3">
         <v>63100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="V54" s="3">
         <v>58000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="W54" s="3">
         <v>8200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="X54" s="3">
         <v>7600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="Y54" s="3">
         <v>7400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Z54" s="3">
         <v>8500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="AA54" s="3">
         <v>7400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="AB54" s="3">
         <v>10100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AC54" s="3">
         <v>8100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AD54" s="3">
         <v>8000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AE54" s="3">
         <v>5700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AF54" s="3">
         <v>5500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AG54" s="3">
         <v>5200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AH54" s="3">
         <v>4600</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +5060,12 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,406 +5097,458 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>18800</v>
+      </c>
+      <c r="F57" s="3">
+        <v>16900</v>
+      </c>
+      <c r="G57" s="3">
+        <v>14700</v>
+      </c>
+      <c r="H57" s="3">
         <v>26500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="I57" s="3">
         <v>31700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="J57" s="3">
         <v>23800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="K57" s="3">
         <v>25400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>22200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>18600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>14900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>10000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>6500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>7900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="R57" s="3">
         <v>7900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="S57" s="3">
         <v>6100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="T57" s="3">
         <v>2800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="U57" s="3">
         <v>2300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="V57" s="3">
         <v>2200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="W57" s="3">
         <v>700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="X57" s="3">
         <v>1100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="Y57" s="3">
         <v>1400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="Z57" s="3">
         <v>2600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="AA57" s="3">
         <v>3800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="AB57" s="3">
         <v>3700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AC57" s="3">
         <v>3300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AD57" s="3">
         <v>3400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AE57" s="3">
         <v>1600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AF57" s="3">
         <v>1300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AG57" s="3">
         <v>1200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AH57" s="3">
         <v>900</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G58" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H58" s="3">
         <v>5200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="I58" s="3">
         <v>5300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="J58" s="3">
         <v>3200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="K58" s="3">
         <v>3900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="L58" s="3">
         <v>2600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="M58" s="3">
         <v>2600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="N58" s="3">
         <v>3500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>4400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="P58" s="3">
         <v>400</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>1000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="W58" s="3">
         <v>7100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="X58" s="3">
         <v>2300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="Y58" s="3">
         <v>6200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="Z58" s="3">
         <v>6000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="AA58" s="3">
         <v>3800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="AB58" s="3">
         <v>4200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AC58" s="3">
         <v>3200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AD58" s="3">
         <v>3400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AE58" s="3">
         <v>3500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AF58" s="3">
         <v>500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AG58" s="3">
         <v>500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AH58" s="3">
         <v>500</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>15800</v>
+      </c>
+      <c r="F59" s="3">
+        <v>17500</v>
+      </c>
+      <c r="G59" s="3">
+        <v>16800</v>
+      </c>
+      <c r="H59" s="3">
         <v>9400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="I59" s="3">
         <v>6300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="J59" s="3">
         <v>4200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="K59" s="3">
         <v>8700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>3100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>7000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>7300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>6700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>6400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="Q59" s="3">
         <v>10200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="R59" s="3">
         <v>12100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="S59" s="3">
         <v>18900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="T59" s="3">
         <v>15400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="U59" s="3">
         <v>11300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="V59" s="3">
         <v>6200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="W59" s="3">
         <v>6800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="X59" s="3">
         <v>6000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="Y59" s="3">
         <v>5400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Z59" s="3">
         <v>5400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="AA59" s="3">
         <v>4800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="AB59" s="3">
         <v>5700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AC59" s="3">
         <v>3900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AD59" s="3">
         <v>4400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AE59" s="3">
         <v>4500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AF59" s="3">
         <v>6400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AG59" s="3">
         <v>5700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AH59" s="3">
         <v>5100</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>43600</v>
+      </c>
+      <c r="F60" s="3">
+        <v>43500</v>
+      </c>
+      <c r="G60" s="3">
+        <v>42300</v>
+      </c>
+      <c r="H60" s="3">
         <v>45700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="I60" s="3">
         <v>48000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="J60" s="3">
         <v>36300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="K60" s="3">
         <v>42100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>31900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>31800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>30900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>24300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>19000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>18200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="R60" s="3">
         <v>20100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="S60" s="3">
         <v>25000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="T60" s="3">
         <v>18200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="U60" s="3">
         <v>13600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="V60" s="3">
         <v>9500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="W60" s="3">
         <v>14500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="X60" s="3">
         <v>9400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="Y60" s="3">
         <v>13000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="Z60" s="3">
         <v>14000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="AA60" s="3">
         <v>12300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="AB60" s="3">
         <v>13500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AC60" s="3">
         <v>10300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AD60" s="3">
         <v>11200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AE60" s="3">
         <v>9600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AF60" s="3">
         <v>8100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AG60" s="3">
         <v>7400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AH60" s="3">
         <v>6400</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>500</v>
+      </c>
+      <c r="F61" s="3">
+        <v>800</v>
+      </c>
+      <c r="G61" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H61" s="3">
         <v>1200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="I61" s="3">
         <v>1200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="J61" s="3">
         <v>1300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="K61" s="3">
         <v>1400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="L61" s="3">
         <v>1700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="M61" s="3">
         <v>1800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="N61" s="3">
         <v>2000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="O61" s="3">
         <v>2000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="P61" s="3">
         <v>900</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4985,46 +5556,58 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>1000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="X61" s="3">
         <v>4800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="Y61" s="3">
         <v>1000</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>1800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AC61" s="3">
         <v>800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AD61" s="3">
         <v>200</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5055,65 +5638,77 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3">
         <v>1600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="R62" s="3">
         <v>800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="S62" s="3">
         <v>1000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="T62" s="3">
         <v>1000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
         <v>100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Z62" s="3">
         <v>100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="AA62" s="3">
         <v>100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="AB62" s="3">
         <v>100</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD62" s="3" t="s">
-        <v>8</v>
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3">
+        <v>0</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5796,20 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5897,20 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,97 +5998,121 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>42100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>44200</v>
+      </c>
+      <c r="F66" s="3">
+        <v>44300</v>
+      </c>
+      <c r="G66" s="3">
+        <v>44100</v>
+      </c>
+      <c r="H66" s="3">
         <v>46800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="I66" s="3">
         <v>49200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="J66" s="3">
         <v>37500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="K66" s="3">
         <v>44300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>34500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>34600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>33800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>27300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>20900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>19800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="R66" s="3">
         <v>20900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="S66" s="3">
         <v>26000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="T66" s="3">
         <v>19200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="U66" s="3">
         <v>13600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="V66" s="3">
         <v>9500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="W66" s="3">
         <v>15600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="X66" s="3">
         <v>14300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="Y66" s="3">
         <v>14000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Z66" s="3">
         <v>14100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="AA66" s="3">
         <v>12400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="AB66" s="3">
         <v>15400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AC66" s="3">
         <v>11100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AD66" s="3">
         <v>11500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AE66" s="3">
         <v>9600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AF66" s="3">
         <v>8100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AG66" s="3">
         <v>7400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AH66" s="3">
         <v>6400</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +6144,12 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +6237,20 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +6338,20 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +6439,20 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,97 +6540,121 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-117800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-113000</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-106800</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-102800</v>
+      </c>
+      <c r="H72" s="3">
         <v>-75600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="I72" s="3">
         <v>-71800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="J72" s="3">
         <v>-68800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="K72" s="3">
         <v>-56800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>-52100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>-48700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>-43300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>-38100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>-33900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>-25300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="R72" s="3">
         <v>-23500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="S72" s="3">
         <v>-22800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="T72" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="U72" s="3">
         <v>-22300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="V72" s="3">
         <v>-23600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="W72" s="3">
         <v>-22000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="X72" s="3">
         <v>-20900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="Y72" s="3">
         <v>-20200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Z72" s="3">
         <v>-18600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="AA72" s="3">
         <v>-16900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="AB72" s="3">
         <v>-14300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AC72" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AD72" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AE72" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AF72" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AG72" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AH72" s="3">
         <v>-5400</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6742,20 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6843,20 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,97 +6944,121 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="F76" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="G76" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="H76" s="3">
         <v>2400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="I76" s="3">
         <v>5800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="J76" s="3">
         <v>8200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="K76" s="3">
         <v>20100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>24200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>26700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>30300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>34700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>37500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>46300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="R76" s="3">
         <v>44600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="S76" s="3">
         <v>48200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="T76" s="3">
         <v>48800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="U76" s="3">
         <v>49500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="V76" s="3">
         <v>48600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="W76" s="3">
         <v>-7400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="X76" s="3">
         <v>-6700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="Y76" s="3">
         <v>-6600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Z76" s="3">
         <v>-5600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="AA76" s="3">
         <v>-5000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="AB76" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AC76" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AD76" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AE76" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AF76" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AG76" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AH76" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +7146,227 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="H80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="V80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="X80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="Y80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Z80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="AA80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="AB80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AC80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AD80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AE80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AF80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AG80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AH80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AI80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-3000</v>
+        <v>-4800</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F81" s="3">
-        <v>-2600</v>
+        <v>-4000</v>
       </c>
       <c r="G81" s="3">
-        <v>-4700</v>
+        <v>-27200</v>
       </c>
       <c r="H81" s="3">
         <v>-3800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="M81" s="3">
         <v>-5800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="N81" s="3">
         <v>-5300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="O81" s="3">
         <v>-4200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="P81" s="3">
         <v>-8700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="Q81" s="3">
         <v>-1700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="R81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="S81" s="3">
         <v>-600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="T81" s="3">
         <v>100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="U81" s="3">
         <v>1300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="V81" s="3">
         <v>-1600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="W81" s="3">
         <v>-1100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="X81" s="3">
         <v>-700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="Y81" s="3">
         <v>-1600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Z81" s="3">
         <v>-1700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="AA81" s="3">
         <v>-2600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="AB81" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AC81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AD81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AE81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AF81" s="3">
         <v>-800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AG81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AH81" s="3">
         <v>-800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AI81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,61 +7398,65 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3">
         <v>300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
+        <v>300</v>
+      </c>
+      <c r="I83" s="3">
+        <v>300</v>
+      </c>
+      <c r="J83" s="3">
         <v>200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
       </c>
       <c r="L83" s="3">
+        <v>200</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
+        <v>100</v>
+      </c>
+      <c r="O83" s="3">
+        <v>100</v>
+      </c>
+      <c r="P83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="3">
         <v>400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="T83" s="3">
         <v>200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>100</v>
-      </c>
-      <c r="S83" s="3">
-        <v>100</v>
-      </c>
-      <c r="T83" s="3">
-        <v>100</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
@@ -6682,22 +7477,34 @@
         <v>100</v>
       </c>
       <c r="AA83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC83" s="3">
         <v>100</v>
       </c>
       <c r="AD83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +7592,20 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7693,20 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7794,20 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7895,20 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,97 +7996,121 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3">
+        <v>600</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="M89" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="O89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="P89" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="R89" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="S89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="T89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U89" s="3">
         <v>1000</v>
       </c>
-      <c r="E89" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="V89" s="3">
+        <v>300</v>
+      </c>
+      <c r="W89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X89" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AE89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="AF89" s="3">
         <v>600</v>
       </c>
-      <c r="G89" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="I89" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>1000</v>
-      </c>
-      <c r="R89" s="3">
-        <v>300</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="T89" s="3">
-        <v>100</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="X89" s="3">
-        <v>1600</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="AG89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>600</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AH89" s="3">
         <v>-900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AI89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,97 +8142,113 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="P91" s="3">
         <v>100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>8</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3">
         <v>-100</v>
       </c>
       <c r="T91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-200</v>
       </c>
       <c r="AC91" s="3">
         <v>-100</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AH91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +8336,20 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,97 +8437,121 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L94" s="3">
+        <v>2100</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H94" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="O94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="P94" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="T94" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="L94" s="3">
-        <v>100</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="AB94" s="3">
         <v>-400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AC94" s="3">
         <v>-500</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>-300</v>
       </c>
       <c r="AD94" s="3">
         <v>-200</v>
       </c>
       <c r="AE94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +8583,12 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7684,17 +8619,17 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7741,8 +8676,20 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8777,20 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8878,20 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,97 +8979,121 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O100" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="S100" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="T100" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="U100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V100" s="3">
+        <v>49400</v>
+      </c>
+      <c r="W100" s="3">
+        <v>600</v>
+      </c>
+      <c r="X100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y100" s="3">
         <v>1200</v>
       </c>
-      <c r="H100" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-500</v>
-      </c>
-      <c r="R100" s="3">
-        <v>49400</v>
-      </c>
-      <c r="S100" s="3">
-        <v>600</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-300</v>
-      </c>
-      <c r="U100" s="3">
-        <v>1200</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="Z100" s="3">
         <v>2000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="AA100" s="3">
         <v>-400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="AB100" s="3">
         <v>1100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AC100" s="3">
         <v>2200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AD100" s="3">
         <v>400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AE100" s="3">
         <v>3000</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AH100" s="3">
         <v>100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AI100" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8129,17 +9124,17 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8186,93 +9181,117 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="K102" s="3">
         <v>-3700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>-3800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>-4700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>-6600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>-4200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>-4300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="R102" s="3">
         <v>-7500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="S102" s="3">
         <v>-5900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="T102" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="U102" s="3">
         <v>500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="V102" s="3">
         <v>49700</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="Y102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="Z102" s="3">
         <v>100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="AA102" s="3">
         <v>-3100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="AB102" s="3">
         <v>2300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AC102" s="3">
         <v>100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AD102" s="3">
         <v>-300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AE102" s="3">
         <v>300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AG102" s="3">
         <v>-600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AH102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AI102" s="3">
         <v>900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UGRO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UGRO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>UGRO</t>
   </si>
@@ -656,455 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
+        <v>500</v>
+      </c>
+      <c r="F8" s="3">
         <v>2400</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="3">
-        <v>9500</v>
-      </c>
       <c r="G8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3">
         <v>8000</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
         <v>15400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>15000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>19600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>18500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>16800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>17300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>12400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>16300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>21100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>19000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>18300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>12800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>12000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>9200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>8400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>4000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>4300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>7100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>5600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>11500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>5800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>5400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>5300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>9300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>3400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
+        <v>200</v>
+      </c>
+      <c r="F9" s="3">
         <v>2600</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="3">
-        <v>8900</v>
-      </c>
-      <c r="G9" s="3">
-        <v>600</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J9" s="3">
         <v>7300</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>12400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>13300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>17200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>15900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>13700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>14100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>9800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>12800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>16200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>14000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>14000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>9900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>9400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>7500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>6700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>3100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>6000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>3700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>7900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>4200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>3900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>3700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>6500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>2400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
+        <v>300</v>
+      </c>
+      <c r="F10" s="3">
         <v>-200</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3">
-        <v>600</v>
-      </c>
-      <c r="G10" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="J10" s="3">
         <v>700</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3">
         <v>3000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>2500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>3000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>3200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>3500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>4900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>5000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>4300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>3600</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>1500</v>
       </c>
       <c r="AF10" s="3">
         <v>1600</v>
       </c>
       <c r="AG10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AI10" s="3">
         <v>2800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>1000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1140,8 +1165,10 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1241,8 +1268,14 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1342,56 +1375,62 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>800</v>
+      </c>
+      <c r="F14" s="3">
         <v>2300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
-        <v>11500</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
+      <c r="I14" s="3">
+        <v>6200</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>1500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>1400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>5000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1399,102 +1438,108 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-1000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>800</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>300</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>500</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
+      <c r="AH14" s="3">
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>200</v>
       </c>
-      <c r="G15" s="3">
-        <v>200</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
+        <v>100</v>
+      </c>
+      <c r="J15" s="3">
         <v>300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>400</v>
-      </c>
-      <c r="J15" s="3">
-        <v>400</v>
-      </c>
-      <c r="K15" s="3">
-        <v>200</v>
       </c>
       <c r="L15" s="3">
         <v>400</v>
       </c>
       <c r="M15" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="N15" s="3">
         <v>400</v>
       </c>
       <c r="O15" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="P15" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Q15" s="3">
         <v>300</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>8</v>
+      <c r="R15" s="3">
+        <v>300</v>
+      </c>
+      <c r="S15" s="3">
+        <v>300</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>8</v>
@@ -1508,11 +1553,11 @@
       <c r="W15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
@@ -1544,8 +1589,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,210 +1629,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F17" s="3">
         <v>4600</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="3">
-        <v>13600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>12400</v>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H17" s="3">
+        <v>600</v>
+      </c>
+      <c r="I17" s="3">
+        <v>8800</v>
+      </c>
+      <c r="J17" s="3">
         <v>11200</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
         <v>17900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>19600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>23100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>22600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>21800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>20300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>16000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>18200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>21900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>19600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>18200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>11600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>12700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>9500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>8500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>5200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>5700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>8900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>7500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>14100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>7200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>7100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>6200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>10600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>4200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2200</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="O18" s="3">
         <v>-4100</v>
       </c>
-      <c r="G18" s="3">
-        <v>-15600</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-5100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-2900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1817,59 +1882,61 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1880,26 +1947,26 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
@@ -1907,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="AF20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG20" s="3">
         <v>0</v>
@@ -1918,151 +1985,163 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>100</v>
       </c>
-      <c r="F21" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-15100</v>
-      </c>
       <c r="H21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="J21" s="3">
         <v>-2900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-4400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-3200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-3900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-4700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-2600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-1400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>-700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>500</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>400</v>
       </c>
       <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -2079,191 +2158,203 @@
         <v>0</v>
       </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>1000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>400</v>
-      </c>
-      <c r="X22" s="3">
-        <v>400</v>
       </c>
       <c r="Y22" s="3">
         <v>400</v>
       </c>
       <c r="Z22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB22" s="3">
         <v>300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>100</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>0</v>
-      </c>
       <c r="AH22" s="3">
         <v>0</v>
       </c>
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-5000</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-27100</v>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="J23" s="3">
         <v>-3500</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
         <v>-2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-4800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-5800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-5300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-4200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-1600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>-1300</v>
       </c>
       <c r="AH23" s="3">
         <v>-800</v>
       </c>
       <c r="AI23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AJ23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AK23" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>100</v>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>8</v>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P24" s="3">
-        <v>-100</v>
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q24" s="3">
         <v>-100</v>
@@ -2272,10 +2363,10 @@
         <v>-100</v>
       </c>
       <c r="S24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -2322,8 +2413,14 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2423,210 +2520,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-5000</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-27200</v>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="J26" s="3">
         <v>-3500</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3">
         <v>-2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-4700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-5800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-5300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-4200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>-1300</v>
       </c>
       <c r="AH26" s="3">
         <v>-800</v>
       </c>
       <c r="AI26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AJ26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AK26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-4800</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3">
         <v>-4000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-27200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3800</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3">
         <v>-2600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-5800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-5300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-4200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>-1300</v>
       </c>
       <c r="AH27" s="3">
         <v>-800</v>
       </c>
       <c r="AI27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AJ27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AK27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2726,32 +2841,38 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>200</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="J29" s="3">
         <v>-300</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
@@ -2827,8 +2948,14 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2928,8 +3055,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3029,59 +3162,65 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="3">
-        <v>500</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -3092,26 +3231,26 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
@@ -3119,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="AF32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG32" s="3">
         <v>0</v>
@@ -3130,109 +3269,121 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4800</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3">
         <v>-4000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-27200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3800</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3">
         <v>-2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-4700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-5800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-5300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-4200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>-1300</v>
       </c>
       <c r="AH33" s="3">
         <v>-800</v>
       </c>
       <c r="AI33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AJ33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AK33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3332,215 +3483,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4800</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3">
         <v>-4000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-27200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3800</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3">
         <v>-2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-4700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-5800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-5300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-4200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>-1300</v>
       </c>
       <c r="AH35" s="3">
         <v>-800</v>
       </c>
       <c r="AI35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AJ35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AK35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3576,8 +3745,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3613,91 +3784,93 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>8600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>7300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>12000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>18600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>22800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>27100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>34600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>40500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>50400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>49900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>200</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>400</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>600</v>
       </c>
       <c r="AA41" s="3">
         <v>400</v>
       </c>
       <c r="AB41" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC41" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD41" s="3">
         <v>3500</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>900</v>
       </c>
       <c r="AE41" s="3">
         <v>1200</v>
@@ -3706,16 +3879,22 @@
         <v>900</v>
       </c>
       <c r="AG41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>900</v>
+      </c>
+      <c r="AI41" s="3">
         <v>1000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>600</v>
       </c>
-      <c r="AI41" s="3" t="s">
+      <c r="AK41" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3815,117 +3994,129 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="3">
         <v>600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>4800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>9200</v>
       </c>
-      <c r="G43" s="3">
-        <v>12500</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J43" s="3">
         <v>28500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>36200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>26400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>34700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>26700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>22400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>24900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>16000</v>
-      </c>
-      <c r="P43" s="3">
-        <v>13500</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>15400</v>
       </c>
       <c r="R43" s="3">
         <v>13500</v>
       </c>
       <c r="S43" s="3">
+        <v>15400</v>
+      </c>
+      <c r="T43" s="3">
+        <v>13500</v>
+      </c>
+      <c r="U43" s="3">
         <v>13100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>5800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>3000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>1100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>1000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>900</v>
       </c>
-      <c r="AI43" s="3" t="s">
+      <c r="AK43" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>200</v>
-      </c>
-      <c r="E44" s="3">
-        <v>200</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F44" s="3">
         <v>200</v>
@@ -3946,10 +4137,10 @@
         <v>200</v>
       </c>
       <c r="L44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N44" s="3">
         <v>300</v>
@@ -3961,49 +4152,49 @@
         <v>300</v>
       </c>
       <c r="Q44" s="3">
+        <v>300</v>
+      </c>
+      <c r="R44" s="3">
+        <v>300</v>
+      </c>
+      <c r="S44" s="3">
         <v>400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>500</v>
-      </c>
-      <c r="T44" s="3">
-        <v>600</v>
-      </c>
-      <c r="U44" s="3">
-        <v>600</v>
       </c>
       <c r="V44" s="3">
         <v>600</v>
       </c>
       <c r="W44" s="3">
+        <v>600</v>
+      </c>
+      <c r="X44" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y44" s="3">
         <v>500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>700</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>1300</v>
       </c>
       <c r="AD44" s="3">
         <v>1000</v>
       </c>
       <c r="AE44" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="AF44" s="3">
         <v>1000</v>
@@ -4012,215 +4203,233 @@
         <v>1200</v>
       </c>
       <c r="AH44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI44" s="3">
         <v>1200</v>
       </c>
-      <c r="AI44" s="3" t="s">
+      <c r="AJ44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AK44" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>1000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>2400</v>
       </c>
-      <c r="G45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J45" s="3">
         <v>3300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>3600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>3300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>4900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>6100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>10100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>11200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>7800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>6200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>3900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>3500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>2700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>2100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>2500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>1900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>1100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>1200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>1000</v>
       </c>
-      <c r="AI45" s="3" t="s">
+      <c r="AK45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3">
         <v>2200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>13400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>15800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>33800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>39400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>29600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>41000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>34800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>34500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>36900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>34600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>37300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>44800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>51000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>59500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>54700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>60300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>55200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>5200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>4600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>4400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>5300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>4000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>7000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>4800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>4900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>3900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>3800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>4300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>3700</v>
       </c>
-      <c r="AI46" s="3" t="s">
+      <c r="AK46" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4251,32 +4460,32 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>2600</v>
-      </c>
-      <c r="N47" s="3">
-        <v>2600</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
         <v>2600</v>
       </c>
       <c r="P47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="R47" s="3">
         <v>2500</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>4200</v>
-      </c>
-      <c r="R47" s="3">
-        <v>4200</v>
       </c>
       <c r="S47" s="3">
         <v>4200</v>
       </c>
       <c r="T47" s="3">
-        <v>1700</v>
+        <v>4200</v>
       </c>
       <c r="U47" s="3">
-        <v>1700</v>
+        <v>4200</v>
       </c>
       <c r="V47" s="3">
         <v>1700</v>
@@ -4291,206 +4500,218 @@
         <v>1700</v>
       </c>
       <c r="Z47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AB47" s="3">
         <v>1800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>2000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>1300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>1700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>1500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>1300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>1100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>500</v>
       </c>
-      <c r="AI47" s="3" t="s">
+      <c r="AK47" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>300</v>
+      </c>
+      <c r="F48" s="3">
         <v>1000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1500</v>
       </c>
-      <c r="G48" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J48" s="3">
         <v>2900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1600</v>
-      </c>
-      <c r="R48" s="3">
-        <v>900</v>
-      </c>
-      <c r="S48" s="3">
-        <v>900</v>
       </c>
       <c r="T48" s="3">
         <v>900</v>
       </c>
       <c r="U48" s="3">
+        <v>900</v>
+      </c>
+      <c r="V48" s="3">
+        <v>900</v>
+      </c>
+      <c r="W48" s="3">
         <v>100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>200</v>
-      </c>
-      <c r="X48" s="3">
-        <v>300</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>300</v>
       </c>
       <c r="Z48" s="3">
         <v>300</v>
       </c>
       <c r="AA48" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC48" s="3">
         <v>400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>300</v>
       </c>
-      <c r="AI48" s="3" t="s">
+      <c r="AK48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>259100</v>
       </c>
       <c r="E49" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
         <v>1200</v>
       </c>
       <c r="H49" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>12600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>12800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>12900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>20000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>20200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>20400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>20700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>21000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>16600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>15500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>9400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>9600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>10600</v>
-      </c>
-      <c r="U49" s="3">
-        <v>900</v>
-      </c>
-      <c r="V49" s="3">
-        <v>900</v>
       </c>
       <c r="W49" s="3">
         <v>900</v>
       </c>
       <c r="X49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="Y49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="Z49" s="3">
         <v>1000</v>
@@ -4502,28 +4723,34 @@
         <v>1000</v>
       </c>
       <c r="AC49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE49" s="3">
         <v>900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>900</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>100</v>
       </c>
       <c r="AG49" s="3">
         <v>100</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI49" s="3" t="s">
+      <c r="AH49" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK49" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4623,8 +4850,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4724,8 +4957,14 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4744,8 +4983,8 @@
       <c r="H52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
+      <c r="I52" s="3">
+        <v>2300</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>8</v>
@@ -4768,51 +5007,51 @@
       <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>8</v>
+      <c r="T52" s="3">
+        <v>0</v>
       </c>
       <c r="U52" s="3">
-        <v>100</v>
-      </c>
-      <c r="V52" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W52" s="3">
         <v>100</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y52" s="3" t="s">
-        <v>8</v>
+      <c r="X52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>100</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>0</v>
+      <c r="AA52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
         <v>100</v>
       </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
       <c r="AF52" s="3">
         <v>0</v>
       </c>
@@ -4820,13 +5059,19 @@
         <v>0</v>
       </c>
       <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>100</v>
       </c>
-      <c r="AI52" s="3" t="s">
+      <c r="AK52" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4926,109 +5171,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>263000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>300</v>
+      </c>
+      <c r="F54" s="3">
         <v>3200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>9900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>16100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>19500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>49200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>55000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>45700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>64400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>58600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>61300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>64100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>62100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>58400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>66100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>65500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>74200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>68000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>63100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>58000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>8200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>7600</v>
-      </c>
-      <c r="Y54" s="3">
-        <v>7400</v>
-      </c>
-      <c r="Z54" s="3">
-        <v>8500</v>
       </c>
       <c r="AA54" s="3">
         <v>7400</v>
       </c>
       <c r="AB54" s="3">
+        <v>8500</v>
+      </c>
+      <c r="AC54" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AD54" s="3">
         <v>10100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>8100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>8000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>5700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>5500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>5200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>4600</v>
       </c>
-      <c r="AI54" s="3" t="s">
+      <c r="AK54" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5064,8 +5321,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5101,460 +5360,486 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>18200</v>
+      </c>
+      <c r="F57" s="3">
         <v>17500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>18800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>16900</v>
       </c>
-      <c r="G57" s="3">
-        <v>14700</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>13500</v>
+      </c>
+      <c r="J57" s="3">
         <v>26500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>31700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>23800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>25400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>22200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>18600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>14900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>10000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>6500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>7900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>7900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>6100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>2200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>2600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>3800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>3700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>3300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>3400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>1600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>1300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>1200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>900</v>
       </c>
-      <c r="AI57" s="3" t="s">
+      <c r="AK57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F58" s="3">
         <v>4100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>4500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>4500</v>
       </c>
-      <c r="G58" s="3">
-        <v>6500</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J58" s="3">
         <v>5200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>3500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>4400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>400</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>1000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>7100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>2300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>6200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>6000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>3800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>4200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>3200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>3400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3500</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>500</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>500</v>
       </c>
       <c r="AH58" s="3">
         <v>500</v>
       </c>
-      <c r="AI58" s="3" t="s">
+      <c r="AI58" s="3">
+        <v>500</v>
+      </c>
+      <c r="AJ58" s="3">
+        <v>500</v>
+      </c>
+      <c r="AK58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>17700</v>
+      </c>
+      <c r="F59" s="3">
         <v>15700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>15800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>17500</v>
       </c>
-      <c r="G59" s="3">
-        <v>16800</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>18600</v>
+      </c>
+      <c r="J59" s="3">
         <v>9400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>6300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>4200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>8700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>7000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>7300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>6700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>6400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>10200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>12100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>18900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>15400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>11300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>6200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>6800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>6000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>5400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>5400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>4800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>5700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>3900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>4400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>4500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>6400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>5700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>5100</v>
       </c>
-      <c r="AI59" s="3" t="s">
+      <c r="AK59" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>45400</v>
+      </c>
+      <c r="F60" s="3">
         <v>41900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>43600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>43500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>42300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>45700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>48000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>36300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>42100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>31900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>31800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>30900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>24300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>19000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>18200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>20100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>25000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>18200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>13600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>9500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>14500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>9400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>13000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>14000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>12300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>13500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>10300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>11200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>9600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>8100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>7400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>6400</v>
       </c>
-      <c r="AI60" s="3" t="s">
+      <c r="AK60" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>100</v>
+      </c>
+      <c r="F61" s="3">
         <v>200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J61" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K61" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L61" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O61" s="3">
         <v>1800</v>
       </c>
-      <c r="H61" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I61" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J61" s="3">
-        <v>1300</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L61" s="3">
-        <v>1700</v>
-      </c>
-      <c r="M61" s="3">
-        <v>1800</v>
-      </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>2000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>900</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -5568,35 +5853,35 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X61" s="3">
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="Y61" s="3">
         <v>1000</v>
       </c>
       <c r="Z61" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="AA61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>1800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>200</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -5606,8 +5891,14 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5626,8 +5917,8 @@
       <c r="H62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
+      <c r="I62" s="3">
+        <v>700</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
@@ -5650,35 +5941,35 @@
       <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S62" s="3">
         <v>1600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1000</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA62" s="3">
         <v>100</v>
@@ -5687,16 +5978,16 @@
         <v>100</v>
       </c>
       <c r="AC62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF62" s="3" t="s">
-        <v>8</v>
+        <v>100</v>
+      </c>
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>0</v>
       </c>
       <c r="AG62" s="3" t="s">
         <v>8</v>
@@ -5707,8 +5998,14 @@
       <c r="AI62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5808,8 +6105,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5909,8 +6212,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6010,109 +6319,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>65900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>45500</v>
+      </c>
+      <c r="F66" s="3">
         <v>42100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>44200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>44300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>44100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>46800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>49200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>37500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>44300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>34500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>34600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>33800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>27300</v>
-      </c>
-      <c r="P66" s="3">
-        <v>20900</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>19800</v>
       </c>
       <c r="R66" s="3">
         <v>20900</v>
       </c>
       <c r="S66" s="3">
+        <v>19800</v>
+      </c>
+      <c r="T66" s="3">
+        <v>20900</v>
+      </c>
+      <c r="U66" s="3">
         <v>26000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>19200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>13600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>9500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>15600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>14300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>14000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>14100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>12400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>15400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>11100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>11500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>9600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>8100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>7400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>6400</v>
       </c>
-      <c r="AI66" s="3" t="s">
+      <c r="AK66" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6148,8 +6469,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6249,8 +6572,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6350,8 +6679,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6451,8 +6786,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6552,109 +6893,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-128100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-124900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-117800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-113000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-106800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-102800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-75600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-71800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-68800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-56800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-52100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-48700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-43300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-38100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-33900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-25300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-23500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-22800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-22200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-22300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-23600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-22000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-20900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-20200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-18600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-16900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-14300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-11400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-8500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-6800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-5400</v>
       </c>
-      <c r="AI72" s="3" t="s">
+      <c r="AK72" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6754,8 +7107,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6855,8 +7214,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6956,109 +7321,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>130300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-45200</v>
+      </c>
+      <c r="F76" s="3">
         <v>-38900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-34200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-28200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-24600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>8200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>20100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>24200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>26700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>30300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>34700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>37500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>46300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>44600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>48200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>48800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>49500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>48600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-7400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-5600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI76" s="3" t="s">
+      <c r="AK76" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7158,215 +7535,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4800</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3">
         <v>-4000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-27200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3800</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3">
         <v>-2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-4700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-5800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-5300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-4200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>-1300</v>
       </c>
       <c r="AH81" s="3">
         <v>-800</v>
       </c>
       <c r="AI81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AJ81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AK81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7402,22 +7797,24 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="3">
-        <v>300</v>
-      </c>
-      <c r="G83" s="3">
-        <v>300</v>
+      <c r="E83" s="3">
+        <v>200</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H83" s="3">
         <v>300</v>
@@ -7426,10 +7823,10 @@
         <v>300</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K83" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
@@ -7438,7 +7835,7 @@
         <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
@@ -7447,22 +7844,22 @@
         <v>100</v>
       </c>
       <c r="Q83" s="3">
+        <v>100</v>
+      </c>
+      <c r="R83" s="3">
+        <v>100</v>
+      </c>
+      <c r="S83" s="3">
         <v>400</v>
-      </c>
-      <c r="R83" s="3">
-        <v>200</v>
-      </c>
-      <c r="S83" s="3">
-        <v>200</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W83" s="3">
         <v>100</v>
@@ -7489,22 +7886,28 @@
         <v>100</v>
       </c>
       <c r="AE83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3">
         <v>100</v>
       </c>
-      <c r="AH83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK83" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7604,8 +8007,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +8114,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7806,8 +8221,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7907,8 +8328,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8008,109 +8435,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="D89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>400</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3">
         <v>2200</v>
       </c>
-      <c r="G89" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="I89" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3">
         <v>600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-4700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-5400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>3000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-3700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8146,109 +8585,117 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="E91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="P91" s="3">
-        <v>100</v>
       </c>
       <c r="Q91" s="3">
         <v>-300</v>
       </c>
       <c r="R91" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-100</v>
       </c>
       <c r="AI91" s="3">
         <v>-100</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK91" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8348,8 +8795,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8449,109 +8902,121 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N94" s="3">
         <v>2100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-3100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-2600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-5700</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8587,8 +9052,10 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8631,11 +9098,11 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
@@ -8688,8 +9155,14 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8789,8 +9262,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8890,8 +9369,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8991,109 +9476,121 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3">
         <v>-2300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1800</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3">
         <v>-1100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>-3800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-3200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>49400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>1200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>2000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>1100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>2200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>3000</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9136,11 +9633,11 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -9193,105 +9690,117 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-4700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-6600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-4300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-7500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-5900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-9900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>49700</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>2300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>900</v>
       </c>
     </row>
